--- a/气象/蒙古气象/蒙古91-20气温统计详细表.xlsx
+++ b/气象/蒙古气象/蒙古91-20气温统计详细表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\蒙古气象\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF1E2181-7328-4437-84B5-A98359C1B325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F8C8B66-D066-4830-B635-B5C4EA7D7E80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{E93861B9-CD70-4C8D-B866-011E4AE1EA5C}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3150" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3150" uniqueCount="460">
   <si>
     <t>Архангай</t>
   </si>
@@ -1268,13 +1268,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>巴彦洪格尔省</t>
-  </si>
-  <si>
-    <t>巴彦洪格尔省</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>布尔干省</t>
   </si>
   <si>
@@ -1585,6 +1578,17 @@
     <t>Улаанбаатар</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>巴彦洪戈尔省</t>
+  </si>
+  <si>
+    <t>托孙臣格勒</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>托孙臣格勒</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1812,12 +1816,6 @@
     <xf numFmtId="176" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1828,6 +1826,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2161,26 +2165,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
@@ -2190,7 +2194,7 @@
         <v>305</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>306</v>
@@ -3818,7 +3822,7 @@
         <v>31</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>405</v>
+        <v>457</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>32</v>
@@ -3872,7 +3876,7 @@
         <v>31</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>405</v>
+        <v>457</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>33</v>
@@ -3926,7 +3930,7 @@
         <v>31</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>405</v>
+        <v>457</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>34</v>
@@ -3980,7 +3984,7 @@
         <v>31</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>405</v>
+        <v>457</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>35</v>
@@ -4034,7 +4038,7 @@
         <v>31</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>405</v>
+        <v>457</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>36</v>
@@ -4088,7 +4092,7 @@
         <v>31</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>405</v>
+        <v>457</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>37</v>
@@ -4142,7 +4146,7 @@
         <v>31</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>405</v>
+        <v>457</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>38</v>
@@ -4196,7 +4200,7 @@
         <v>31</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>405</v>
+        <v>457</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>39</v>
@@ -4250,7 +4254,7 @@
         <v>31</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>405</v>
+        <v>457</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>40</v>
@@ -4304,7 +4308,7 @@
         <v>31</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>405</v>
+        <v>457</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>31</v>
@@ -4358,7 +4362,7 @@
         <v>31</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>405</v>
+        <v>457</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>41</v>
@@ -4412,7 +4416,7 @@
         <v>31</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>405</v>
+        <v>457</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>42</v>
@@ -4466,7 +4470,7 @@
         <v>31</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>405</v>
+        <v>457</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>43</v>
@@ -4520,7 +4524,7 @@
         <v>31</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>405</v>
+        <v>457</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>44</v>
@@ -4574,7 +4578,7 @@
         <v>31</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>405</v>
+        <v>457</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>45</v>
@@ -4628,7 +4632,7 @@
         <v>31</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>405</v>
+        <v>457</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>46</v>
@@ -4684,7 +4688,7 @@
         <v>31</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>405</v>
+        <v>457</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>47</v>
@@ -4740,7 +4744,7 @@
         <v>31</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>405</v>
+        <v>457</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>48</v>
@@ -4796,7 +4800,7 @@
         <v>31</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>405</v>
+        <v>457</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>49</v>
@@ -4852,7 +4856,7 @@
         <v>1</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>50</v>
@@ -4908,7 +4912,7 @@
         <v>1</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>48</v>
@@ -4962,7 +4966,7 @@
         <v>1</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>51</v>
@@ -5016,7 +5020,7 @@
         <v>1</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>25</v>
@@ -5072,7 +5076,7 @@
         <v>1</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>52</v>
@@ -5126,7 +5130,7 @@
         <v>1</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>53</v>
@@ -5180,7 +5184,7 @@
         <v>1</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>54</v>
@@ -5234,7 +5238,7 @@
         <v>1</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>55</v>
@@ -5288,7 +5292,7 @@
         <v>1</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>56</v>
@@ -5342,7 +5346,7 @@
         <v>1</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>1</v>
@@ -5396,7 +5400,7 @@
         <v>1</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>57</v>
@@ -5450,7 +5454,7 @@
         <v>1</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>58</v>
@@ -5504,7 +5508,7 @@
         <v>1</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>59</v>
@@ -5558,7 +5562,7 @@
         <v>1</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>60</v>
@@ -5612,7 +5616,7 @@
         <v>1</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>61</v>
@@ -5666,7 +5670,7 @@
         <v>1</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>62</v>
@@ -5722,7 +5726,7 @@
         <v>63</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>64</v>
@@ -5776,7 +5780,7 @@
         <v>63</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>65</v>
@@ -5830,7 +5834,7 @@
         <v>63</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>66</v>
@@ -5884,7 +5888,7 @@
         <v>63</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>58</v>
@@ -5938,7 +5942,7 @@
         <v>63</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>67</v>
@@ -5992,7 +5996,7 @@
         <v>63</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>68</v>
@@ -6046,7 +6050,7 @@
         <v>63</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>69</v>
@@ -6100,7 +6104,7 @@
         <v>63</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>70</v>
@@ -6154,7 +6158,7 @@
         <v>63</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>71</v>
@@ -6208,7 +6212,7 @@
         <v>63</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>72</v>
@@ -6262,7 +6266,7 @@
         <v>63</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>73</v>
@@ -6316,7 +6320,7 @@
         <v>63</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>74</v>
@@ -6370,7 +6374,7 @@
         <v>63</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>75</v>
@@ -6424,7 +6428,7 @@
         <v>63</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>76</v>
@@ -6478,7 +6482,7 @@
         <v>63</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>77</v>
@@ -6532,7 +6536,7 @@
         <v>63</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>78</v>
@@ -6586,7 +6590,7 @@
         <v>63</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>79</v>
@@ -6640,7 +6644,7 @@
         <v>63</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>80</v>
@@ -6694,7 +6698,7 @@
         <v>63</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>81</v>
@@ -6748,7 +6752,7 @@
         <v>63</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>82</v>
@@ -6799,10 +6803,10 @@
         <v>85</v>
       </c>
       <c r="B87" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="C87" s="6" t="s">
         <v>410</v>
-      </c>
-      <c r="C87" s="6" t="s">
-        <v>412</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>84</v>
@@ -6856,7 +6860,7 @@
         <v>85</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>86</v>
@@ -6910,7 +6914,7 @@
         <v>85</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>87</v>
@@ -6966,7 +6970,7 @@
         <v>85</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>88</v>
@@ -7020,7 +7024,7 @@
         <v>85</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>89</v>
@@ -7071,10 +7075,10 @@
         <v>90</v>
       </c>
       <c r="B92" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="C92" s="6" t="s">
         <v>415</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>417</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>91</v>
@@ -7128,7 +7132,7 @@
         <v>90</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>92</v>
@@ -7182,7 +7186,7 @@
         <v>90</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>93</v>
@@ -7236,7 +7240,7 @@
         <v>90</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>94</v>
@@ -7290,7 +7294,7 @@
         <v>90</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>95</v>
@@ -7344,7 +7348,7 @@
         <v>90</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>96</v>
@@ -7398,7 +7402,7 @@
         <v>90</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>97</v>
@@ -7452,7 +7456,7 @@
         <v>90</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>98</v>
@@ -7506,7 +7510,7 @@
         <v>90</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>99</v>
@@ -7560,7 +7564,7 @@
         <v>90</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>100</v>
@@ -7614,7 +7618,7 @@
         <v>90</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>101</v>
@@ -7668,7 +7672,7 @@
         <v>90</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>102</v>
@@ -7722,7 +7726,7 @@
         <v>90</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>103</v>
@@ -7776,7 +7780,7 @@
         <v>104</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>105</v>
@@ -7827,10 +7831,10 @@
         <v>104</v>
       </c>
       <c r="B106" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="C106" s="6" t="s">
         <v>418</v>
-      </c>
-      <c r="C106" s="6" t="s">
-        <v>420</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>106</v>
@@ -7884,7 +7888,7 @@
         <v>104</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>107</v>
@@ -7938,7 +7942,7 @@
         <v>104</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>105</v>
@@ -7992,7 +7996,7 @@
         <v>104</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>108</v>
@@ -8046,7 +8050,7 @@
         <v>104</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>1</v>
@@ -8100,7 +8104,7 @@
         <v>104</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>109</v>
@@ -8154,7 +8158,7 @@
         <v>104</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D112" s="1" t="s">
         <v>110</v>
@@ -8208,7 +8212,7 @@
         <v>104</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>111</v>
@@ -8262,7 +8266,7 @@
         <v>104</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>112</v>
@@ -8316,7 +8320,7 @@
         <v>104</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>113</v>
@@ -8370,7 +8374,7 @@
         <v>104</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>114</v>
@@ -8424,7 +8428,7 @@
         <v>104</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>115</v>
@@ -8478,7 +8482,7 @@
         <v>104</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>116</v>
@@ -8532,7 +8536,7 @@
         <v>104</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>117</v>
@@ -8583,10 +8587,10 @@
         <v>118</v>
       </c>
       <c r="B120" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="C120" s="6" t="s">
         <v>421</v>
-      </c>
-      <c r="C120" s="6" t="s">
-        <v>423</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>13</v>
@@ -8640,7 +8644,7 @@
         <v>118</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>119</v>
@@ -8694,7 +8698,7 @@
         <v>118</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>120</v>
@@ -8748,7 +8752,7 @@
         <v>118</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>121</v>
@@ -8802,7 +8806,7 @@
         <v>118</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>122</v>
@@ -8856,7 +8860,7 @@
         <v>118</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>123</v>
@@ -8910,7 +8914,7 @@
         <v>118</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>124</v>
@@ -8964,7 +8968,7 @@
         <v>118</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>125</v>
@@ -9018,7 +9022,7 @@
         <v>118</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D128" s="1" t="s">
         <v>126</v>
@@ -9072,7 +9076,7 @@
         <v>118</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>127</v>
@@ -9126,7 +9130,7 @@
         <v>118</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>128</v>
@@ -9180,7 +9184,7 @@
         <v>118</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>129</v>
@@ -9234,7 +9238,7 @@
         <v>118</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>130</v>
@@ -9288,7 +9292,7 @@
         <v>118</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>131</v>
@@ -9342,7 +9346,7 @@
         <v>132</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>133</v>
@@ -9398,7 +9402,7 @@
         <v>132</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>134</v>
@@ -9454,7 +9458,7 @@
         <v>132</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>135</v>
@@ -9510,7 +9514,7 @@
         <v>132</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D137" s="1" t="s">
         <v>136</v>
@@ -9566,7 +9570,7 @@
         <v>132</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>137</v>
@@ -9620,7 +9624,7 @@
         <v>132</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>138</v>
@@ -9674,7 +9678,7 @@
         <v>132</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>139</v>
@@ -9730,7 +9734,7 @@
         <v>132</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>140</v>
@@ -9786,7 +9790,7 @@
         <v>132</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>141</v>
@@ -9842,7 +9846,7 @@
         <v>132</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D143" s="1" t="s">
         <v>142</v>
@@ -9898,7 +9902,7 @@
         <v>132</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D144" s="1" t="s">
         <v>143</v>
@@ -9954,7 +9958,7 @@
         <v>132</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D145" s="1" t="s">
         <v>144</v>
@@ -10010,7 +10014,7 @@
         <v>132</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D146" s="1" t="s">
         <v>145</v>
@@ -10066,7 +10070,7 @@
         <v>132</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D147" s="1" t="s">
         <v>146</v>
@@ -10122,7 +10126,7 @@
         <v>132</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D148" s="1" t="s">
         <v>147</v>
@@ -10178,13 +10182,13 @@
         <v>132</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>148</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>348</v>
+        <v>458</v>
       </c>
       <c r="F149" s="2">
         <v>-31.5</v>
@@ -10234,7 +10238,7 @@
         <v>132</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D150" s="1" t="s">
         <v>149</v>
@@ -10290,7 +10294,7 @@
         <v>132</v>
       </c>
       <c r="C151" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D151" s="1" t="s">
         <v>150</v>
@@ -10346,7 +10350,7 @@
         <v>132</v>
       </c>
       <c r="C152" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D152" s="1" t="s">
         <v>151</v>
@@ -10402,7 +10406,7 @@
         <v>132</v>
       </c>
       <c r="C153" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D153" s="1" t="s">
         <v>152</v>
@@ -10456,7 +10460,7 @@
         <v>132</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D154" s="1" t="s">
         <v>153</v>
@@ -10512,7 +10516,7 @@
         <v>132</v>
       </c>
       <c r="C155" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D155" s="1" t="s">
         <v>154</v>
@@ -10568,7 +10572,7 @@
         <v>132</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D156" s="1" t="s">
         <v>155</v>
@@ -10621,10 +10625,10 @@
         <v>155</v>
       </c>
       <c r="B157" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="C157" s="6" t="s">
         <v>427</v>
-      </c>
-      <c r="C157" s="6" t="s">
-        <v>429</v>
       </c>
       <c r="D157" s="1" t="s">
         <v>156</v>
@@ -10678,7 +10682,7 @@
         <v>55</v>
       </c>
       <c r="C158" s="6" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D158" s="1" t="s">
         <v>157</v>
@@ -10729,10 +10733,10 @@
         <v>157</v>
       </c>
       <c r="B159" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="C159" s="6" t="s">
         <v>430</v>
-      </c>
-      <c r="C159" s="6" t="s">
-        <v>432</v>
       </c>
       <c r="D159" s="1" t="s">
         <v>159</v>
@@ -10786,7 +10790,7 @@
         <v>158</v>
       </c>
       <c r="C160" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D160" s="1" t="s">
         <v>36</v>
@@ -10840,7 +10844,7 @@
         <v>158</v>
       </c>
       <c r="C161" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D161" s="1" t="s">
         <v>160</v>
@@ -10894,7 +10898,7 @@
         <v>158</v>
       </c>
       <c r="C162" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D162" s="1" t="s">
         <v>161</v>
@@ -10948,7 +10952,7 @@
         <v>158</v>
       </c>
       <c r="C163" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D163" s="1" t="s">
         <v>71</v>
@@ -11002,7 +11006,7 @@
         <v>158</v>
       </c>
       <c r="C164" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D164" s="1" t="s">
         <v>162</v>
@@ -11056,7 +11060,7 @@
         <v>158</v>
       </c>
       <c r="C165" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D165" s="1" t="s">
         <v>163</v>
@@ -11110,7 +11114,7 @@
         <v>158</v>
       </c>
       <c r="C166" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D166" s="1" t="s">
         <v>164</v>
@@ -11164,7 +11168,7 @@
         <v>158</v>
       </c>
       <c r="C167" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D167" s="1" t="s">
         <v>165</v>
@@ -11218,7 +11222,7 @@
         <v>158</v>
       </c>
       <c r="C168" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D168" s="1" t="s">
         <v>166</v>
@@ -11272,7 +11276,7 @@
         <v>158</v>
       </c>
       <c r="C169" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D169" s="1" t="s">
         <v>167</v>
@@ -11326,7 +11330,7 @@
         <v>158</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D170" s="1" t="s">
         <v>168</v>
@@ -11380,7 +11384,7 @@
         <v>158</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D171" s="1" t="s">
         <v>169</v>
@@ -11434,7 +11438,7 @@
         <v>158</v>
       </c>
       <c r="C172" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D172" s="1" t="s">
         <v>170</v>
@@ -11488,7 +11492,7 @@
         <v>158</v>
       </c>
       <c r="C173" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D173" s="1" t="s">
         <v>171</v>
@@ -11542,7 +11546,7 @@
         <v>158</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D174" s="1" t="s">
         <v>172</v>
@@ -11596,7 +11600,7 @@
         <v>158</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D175" s="1" t="s">
         <v>173</v>
@@ -11650,7 +11654,7 @@
         <v>158</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D176" s="1" t="s">
         <v>174</v>
@@ -11704,7 +11708,7 @@
         <v>175</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D177" s="1" t="s">
         <v>176</v>
@@ -11758,7 +11762,7 @@
         <v>175</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D178" s="1" t="s">
         <v>177</v>
@@ -11812,7 +11816,7 @@
         <v>175</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D179" s="1" t="s">
         <v>178</v>
@@ -11866,7 +11870,7 @@
         <v>175</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D180" s="1" t="s">
         <v>179</v>
@@ -11920,7 +11924,7 @@
         <v>175</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D181" s="1" t="s">
         <v>180</v>
@@ -11976,7 +11980,7 @@
         <v>175</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D182" s="1" t="s">
         <v>181</v>
@@ -12030,7 +12034,7 @@
         <v>175</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D183" s="1" t="s">
         <v>182</v>
@@ -12084,7 +12088,7 @@
         <v>175</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D184" s="1" t="s">
         <v>183</v>
@@ -12138,7 +12142,7 @@
         <v>175</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D185" s="1" t="s">
         <v>184</v>
@@ -12192,7 +12196,7 @@
         <v>175</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D186" s="1" t="s">
         <v>185</v>
@@ -12246,7 +12250,7 @@
         <v>175</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D187" s="1" t="s">
         <v>186</v>
@@ -12300,7 +12304,7 @@
         <v>175</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D188" s="1" t="s">
         <v>187</v>
@@ -12354,7 +12358,7 @@
         <v>175</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D189" s="1" t="s">
         <v>188</v>
@@ -12408,7 +12412,7 @@
         <v>175</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D190" s="1" t="s">
         <v>189</v>
@@ -12459,10 +12463,10 @@
         <v>189</v>
       </c>
       <c r="B191" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="C191" s="6" t="s">
         <v>435</v>
-      </c>
-      <c r="C191" s="6" t="s">
-        <v>437</v>
       </c>
       <c r="D191" s="1" t="s">
         <v>191</v>
@@ -12516,7 +12520,7 @@
         <v>190</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D192" s="1" t="s">
         <v>192</v>
@@ -12570,7 +12574,7 @@
         <v>190</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D193" s="1" t="s">
         <v>193</v>
@@ -12624,7 +12628,7 @@
         <v>190</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D194" s="1" t="s">
         <v>194</v>
@@ -12678,7 +12682,7 @@
         <v>190</v>
       </c>
       <c r="C195" s="6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D195" s="1" t="s">
         <v>195</v>
@@ -12732,7 +12736,7 @@
         <v>190</v>
       </c>
       <c r="C196" s="6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D196" s="1" t="s">
         <v>196</v>
@@ -12786,7 +12790,7 @@
         <v>190</v>
       </c>
       <c r="C197" s="6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D197" s="1" t="s">
         <v>197</v>
@@ -12840,7 +12844,7 @@
         <v>190</v>
       </c>
       <c r="C198" s="6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D198" s="1" t="s">
         <v>198</v>
@@ -12894,7 +12898,7 @@
         <v>190</v>
       </c>
       <c r="C199" s="6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D199" s="1" t="s">
         <v>199</v>
@@ -12948,7 +12952,7 @@
         <v>190</v>
       </c>
       <c r="C200" s="6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D200" s="1" t="s">
         <v>200</v>
@@ -13002,7 +13006,7 @@
         <v>190</v>
       </c>
       <c r="C201" s="6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D201" s="1" t="s">
         <v>190</v>
@@ -13056,7 +13060,7 @@
         <v>190</v>
       </c>
       <c r="C202" s="6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D202" s="1" t="s">
         <v>201</v>
@@ -13110,7 +13114,7 @@
         <v>190</v>
       </c>
       <c r="C203" s="6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D203" s="1" t="s">
         <v>202</v>
@@ -13164,7 +13168,7 @@
         <v>203</v>
       </c>
       <c r="C204" s="6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D204" s="1" t="s">
         <v>204</v>
@@ -13218,7 +13222,7 @@
         <v>203</v>
       </c>
       <c r="C205" s="6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D205" s="1" t="s">
         <v>205</v>
@@ -13274,7 +13278,7 @@
         <v>203</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D206" s="1" t="s">
         <v>206</v>
@@ -13328,7 +13332,7 @@
         <v>203</v>
       </c>
       <c r="C207" s="6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D207" s="1" t="s">
         <v>207</v>
@@ -13382,13 +13386,13 @@
         <v>203</v>
       </c>
       <c r="C208" s="6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="F208" s="2">
         <v>-25.2</v>
@@ -13438,7 +13442,7 @@
         <v>203</v>
       </c>
       <c r="C209" s="6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D209" s="1" t="s">
         <v>208</v>
@@ -13492,7 +13496,7 @@
         <v>203</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D210" s="1" t="s">
         <v>209</v>
@@ -13546,7 +13550,7 @@
         <v>203</v>
       </c>
       <c r="C211" s="6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D211" s="1" t="s">
         <v>210</v>
@@ -13602,7 +13606,7 @@
         <v>203</v>
       </c>
       <c r="C212" s="6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D212" s="1" t="s">
         <v>211</v>
@@ -13658,7 +13662,7 @@
         <v>203</v>
       </c>
       <c r="C213" s="6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D213" s="1" t="s">
         <v>212</v>
@@ -13714,7 +13718,7 @@
         <v>203</v>
       </c>
       <c r="C214" s="6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D214" s="1" t="s">
         <v>190</v>
@@ -13768,7 +13772,7 @@
         <v>203</v>
       </c>
       <c r="C215" s="6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D215" s="1" t="s">
         <v>213</v>
@@ -13824,7 +13828,7 @@
         <v>203</v>
       </c>
       <c r="C216" s="6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D216" s="1" t="s">
         <v>214</v>
@@ -13875,10 +13879,10 @@
         <v>215</v>
       </c>
       <c r="B217" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="C217" s="6" t="s">
         <v>441</v>
-      </c>
-      <c r="C217" s="6" t="s">
-        <v>443</v>
       </c>
       <c r="D217" s="1" t="s">
         <v>216</v>
@@ -13932,7 +13936,7 @@
         <v>215</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D218" s="1" t="s">
         <v>217</v>
@@ -13986,7 +13990,7 @@
         <v>215</v>
       </c>
       <c r="C219" s="6" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D219" s="1" t="s">
         <v>218</v>
@@ -14040,7 +14044,7 @@
         <v>215</v>
       </c>
       <c r="C220" s="6" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D220" s="1" t="s">
         <v>219</v>
@@ -14094,7 +14098,7 @@
         <v>215</v>
       </c>
       <c r="C221" s="6" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D221" s="1" t="s">
         <v>126</v>
@@ -14150,7 +14154,7 @@
         <v>215</v>
       </c>
       <c r="C222" s="6" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D222" s="1" t="s">
         <v>220</v>
@@ -14204,7 +14208,7 @@
         <v>215</v>
       </c>
       <c r="C223" s="6" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D223" s="1" t="s">
         <v>221</v>
@@ -14260,7 +14264,7 @@
         <v>215</v>
       </c>
       <c r="C224" s="6" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D224" s="1" t="s">
         <v>222</v>
@@ -14314,7 +14318,7 @@
         <v>215</v>
       </c>
       <c r="C225" s="6" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D225" s="1" t="s">
         <v>223</v>
@@ -14368,7 +14372,7 @@
         <v>215</v>
       </c>
       <c r="C226" s="6" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D226" s="1" t="s">
         <v>66</v>
@@ -14424,7 +14428,7 @@
         <v>215</v>
       </c>
       <c r="C227" s="6" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D227" s="1" t="s">
         <v>37</v>
@@ -14478,7 +14482,7 @@
         <v>215</v>
       </c>
       <c r="C228" s="6" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D228" s="1" t="s">
         <v>224</v>
@@ -14534,7 +14538,7 @@
         <v>215</v>
       </c>
       <c r="C229" s="6" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D229" s="1" t="s">
         <v>225</v>
@@ -14588,7 +14592,7 @@
         <v>215</v>
       </c>
       <c r="C230" s="6" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D230" s="1" t="s">
         <v>226</v>
@@ -14642,7 +14646,7 @@
         <v>215</v>
       </c>
       <c r="C231" s="6" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D231" s="1" t="s">
         <v>227</v>
@@ -14696,7 +14700,7 @@
         <v>215</v>
       </c>
       <c r="C232" s="6" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D232" s="1" t="s">
         <v>228</v>
@@ -14750,7 +14754,7 @@
         <v>215</v>
       </c>
       <c r="C233" s="6" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D233" s="1" t="s">
         <v>229</v>
@@ -14804,7 +14808,7 @@
         <v>215</v>
       </c>
       <c r="C234" s="6" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D234" s="1" t="s">
         <v>230</v>
@@ -14858,7 +14862,7 @@
         <v>215</v>
       </c>
       <c r="C235" s="6" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D235" s="1" t="s">
         <v>231</v>
@@ -14912,7 +14916,7 @@
         <v>215</v>
       </c>
       <c r="C236" s="6" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D236" s="1" t="s">
         <v>232</v>
@@ -14968,7 +14972,7 @@
         <v>215</v>
       </c>
       <c r="C237" s="6" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D237" s="1" t="s">
         <v>8</v>
@@ -15022,7 +15026,7 @@
         <v>233</v>
       </c>
       <c r="C238" s="6" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D238" s="1" t="s">
         <v>132</v>
@@ -15078,7 +15082,7 @@
         <v>233</v>
       </c>
       <c r="C239" s="6" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D239" s="1" t="s">
         <v>29</v>
@@ -15134,7 +15138,7 @@
         <v>233</v>
       </c>
       <c r="C240" s="6" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D240" s="1" t="s">
         <v>234</v>
@@ -15190,7 +15194,7 @@
         <v>233</v>
       </c>
       <c r="C241" s="6" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D241" s="1" t="s">
         <v>235</v>
@@ -15246,7 +15250,7 @@
         <v>233</v>
       </c>
       <c r="C242" s="6" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D242" s="1" t="s">
         <v>236</v>
@@ -15302,7 +15306,7 @@
         <v>233</v>
       </c>
       <c r="C243" s="6" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D243" s="1" t="s">
         <v>237</v>
@@ -15358,7 +15362,7 @@
         <v>233</v>
       </c>
       <c r="C244" s="6" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D244" s="1" t="s">
         <v>238</v>
@@ -15414,7 +15418,7 @@
         <v>233</v>
       </c>
       <c r="C245" s="6" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D245" s="1" t="s">
         <v>136</v>
@@ -15470,7 +15474,7 @@
         <v>233</v>
       </c>
       <c r="C246" s="6" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D246" s="1" t="s">
         <v>239</v>
@@ -15526,7 +15530,7 @@
         <v>233</v>
       </c>
       <c r="C247" s="6" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D247" s="1" t="s">
         <v>240</v>
@@ -15582,7 +15586,7 @@
         <v>233</v>
       </c>
       <c r="C248" s="6" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D248" s="1" t="s">
         <v>241</v>
@@ -15638,7 +15642,7 @@
         <v>233</v>
       </c>
       <c r="C249" s="6" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D249" s="1" t="s">
         <v>242</v>
@@ -15694,7 +15698,7 @@
         <v>233</v>
       </c>
       <c r="C250" s="6" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D250" s="1" t="s">
         <v>243</v>
@@ -15750,7 +15754,7 @@
         <v>233</v>
       </c>
       <c r="C251" s="6" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D251" s="1" t="s">
         <v>244</v>
@@ -15806,7 +15810,7 @@
         <v>233</v>
       </c>
       <c r="C252" s="6" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D252" s="1" t="s">
         <v>245</v>
@@ -15862,7 +15866,7 @@
         <v>233</v>
       </c>
       <c r="C253" s="6" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D253" s="1" t="s">
         <v>246</v>
@@ -15918,7 +15922,7 @@
         <v>233</v>
       </c>
       <c r="C254" s="6" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D254" s="1" t="s">
         <v>155</v>
@@ -15974,7 +15978,7 @@
         <v>233</v>
       </c>
       <c r="C255" s="6" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D255" s="1" t="s">
         <v>247</v>
@@ -16030,7 +16034,7 @@
         <v>248</v>
       </c>
       <c r="C256" s="6" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D256" s="1" t="s">
         <v>249</v>
@@ -16084,7 +16088,7 @@
         <v>248</v>
       </c>
       <c r="C257" s="6" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D257" s="1" t="s">
         <v>13</v>
@@ -16138,7 +16142,7 @@
         <v>248</v>
       </c>
       <c r="C258" s="6" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D258" s="1" t="s">
         <v>250</v>
@@ -16192,7 +16196,7 @@
         <v>248</v>
       </c>
       <c r="C259" s="6" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D259" s="1" t="s">
         <v>248</v>
@@ -16248,7 +16252,7 @@
         <v>248</v>
       </c>
       <c r="C260" s="6" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D260" s="1" t="s">
         <v>251</v>
@@ -16302,7 +16306,7 @@
         <v>248</v>
       </c>
       <c r="C261" s="6" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D261" s="1" t="s">
         <v>252</v>
@@ -16356,7 +16360,7 @@
         <v>253</v>
       </c>
       <c r="C262" s="6" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D262" s="1" t="s">
         <v>254</v>
@@ -16410,7 +16414,7 @@
         <v>253</v>
       </c>
       <c r="C263" s="6" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D263" s="1" t="s">
         <v>255</v>
@@ -16464,7 +16468,7 @@
         <v>253</v>
       </c>
       <c r="C264" s="6" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D264" s="1" t="s">
         <v>256</v>
@@ -16518,7 +16522,7 @@
         <v>253</v>
       </c>
       <c r="C265" s="6" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D265" s="1" t="s">
         <v>257</v>
@@ -16574,7 +16578,7 @@
         <v>253</v>
       </c>
       <c r="C266" s="6" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D266" s="1" t="s">
         <v>258</v>
@@ -16628,7 +16632,7 @@
         <v>253</v>
       </c>
       <c r="C267" s="6" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D267" s="1" t="s">
         <v>259</v>
@@ -16682,7 +16686,7 @@
         <v>253</v>
       </c>
       <c r="C268" s="6" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D268" s="1" t="s">
         <v>77</v>
@@ -16736,7 +16740,7 @@
         <v>253</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D269" s="1" t="s">
         <v>260</v>
@@ -16790,7 +16794,7 @@
         <v>253</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D270" s="1" t="s">
         <v>261</v>
@@ -16844,7 +16848,7 @@
         <v>253</v>
       </c>
       <c r="C271" s="6" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D271" s="1" t="s">
         <v>262</v>
@@ -16898,7 +16902,7 @@
         <v>253</v>
       </c>
       <c r="C272" s="6" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D272" s="1" t="s">
         <v>263</v>
@@ -16954,7 +16958,7 @@
         <v>253</v>
       </c>
       <c r="C273" s="6" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D273" s="1" t="s">
         <v>264</v>
@@ -17008,7 +17012,7 @@
         <v>253</v>
       </c>
       <c r="C274" s="6" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D274" s="1" t="s">
         <v>265</v>
@@ -17062,7 +17066,7 @@
         <v>253</v>
       </c>
       <c r="C275" s="6" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D275" s="1" t="s">
         <v>266</v>
@@ -17116,7 +17120,7 @@
         <v>253</v>
       </c>
       <c r="C276" s="6" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D276" s="1" t="s">
         <v>267</v>
@@ -17172,7 +17176,7 @@
         <v>253</v>
       </c>
       <c r="C277" s="6" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D277" s="1" t="s">
         <v>68</v>
@@ -17226,7 +17230,7 @@
         <v>93</v>
       </c>
       <c r="C278" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D278" s="1" t="s">
         <v>268</v>
@@ -17282,7 +17286,7 @@
         <v>93</v>
       </c>
       <c r="C279" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D279" s="1" t="s">
         <v>269</v>
@@ -17336,7 +17340,7 @@
         <v>93</v>
       </c>
       <c r="C280" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D280" s="1" t="s">
         <v>270</v>
@@ -17390,7 +17394,7 @@
         <v>93</v>
       </c>
       <c r="C281" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D281" s="1" t="s">
         <v>50</v>
@@ -17444,7 +17448,7 @@
         <v>93</v>
       </c>
       <c r="C282" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D282" s="1" t="s">
         <v>271</v>
@@ -17498,7 +17502,7 @@
         <v>93</v>
       </c>
       <c r="C283" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D283" s="1" t="s">
         <v>148</v>
@@ -17554,7 +17558,7 @@
         <v>93</v>
       </c>
       <c r="C284" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D284" s="1" t="s">
         <v>149</v>
@@ -17608,7 +17612,7 @@
         <v>93</v>
       </c>
       <c r="C285" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D285" s="1" t="s">
         <v>272</v>
@@ -17662,7 +17666,7 @@
         <v>93</v>
       </c>
       <c r="C286" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D286" s="1" t="s">
         <v>273</v>
@@ -17716,7 +17720,7 @@
         <v>93</v>
       </c>
       <c r="C287" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D287" s="1" t="s">
         <v>274</v>
@@ -17772,7 +17776,7 @@
         <v>93</v>
       </c>
       <c r="C288" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D288" s="1" t="s">
         <v>275</v>
@@ -17828,7 +17832,7 @@
         <v>93</v>
       </c>
       <c r="C289" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D289" s="1" t="s">
         <v>276</v>
@@ -17882,7 +17886,7 @@
         <v>93</v>
       </c>
       <c r="C290" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D290" s="1" t="s">
         <v>277</v>
@@ -17938,7 +17942,7 @@
         <v>93</v>
       </c>
       <c r="C291" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D291" s="1" t="s">
         <v>278</v>
@@ -17994,7 +17998,7 @@
         <v>93</v>
       </c>
       <c r="C292" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D292" s="1" t="s">
         <v>279</v>
@@ -18050,7 +18054,7 @@
         <v>93</v>
       </c>
       <c r="C293" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D293" s="1" t="s">
         <v>280</v>
@@ -18106,7 +18110,7 @@
         <v>93</v>
       </c>
       <c r="C294" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D294" s="1" t="s">
         <v>281</v>
@@ -18162,7 +18166,7 @@
         <v>93</v>
       </c>
       <c r="C295" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D295" s="1" t="s">
         <v>282</v>
@@ -18218,7 +18222,7 @@
         <v>93</v>
       </c>
       <c r="C296" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D296" s="1" t="s">
         <v>283</v>
@@ -18274,7 +18278,7 @@
         <v>93</v>
       </c>
       <c r="C297" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D297" s="1" t="s">
         <v>284</v>
@@ -18328,7 +18332,7 @@
         <v>93</v>
       </c>
       <c r="C298" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D298" s="1" t="s">
         <v>285</v>
@@ -18384,7 +18388,7 @@
         <v>93</v>
       </c>
       <c r="C299" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D299" s="1" t="s">
         <v>286</v>
@@ -18440,7 +18444,7 @@
         <v>93</v>
       </c>
       <c r="C300" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D300" s="1" t="s">
         <v>213</v>
@@ -18496,7 +18500,7 @@
         <v>93</v>
       </c>
       <c r="C301" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D301" s="1" t="s">
         <v>287</v>
@@ -18549,10 +18553,10 @@
         <v>300</v>
       </c>
       <c r="B302" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="C302" s="6" t="s">
         <v>452</v>
-      </c>
-      <c r="C302" s="6" t="s">
-        <v>454</v>
       </c>
       <c r="D302" s="1" t="s">
         <v>289</v>
@@ -18606,7 +18610,7 @@
         <v>288</v>
       </c>
       <c r="C303" s="6" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D303" s="1" t="s">
         <v>290</v>
@@ -18660,7 +18664,7 @@
         <v>288</v>
       </c>
       <c r="C304" s="6" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D304" s="1" t="s">
         <v>291</v>
@@ -18714,7 +18718,7 @@
         <v>288</v>
       </c>
       <c r="C305" s="6" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D305" s="1" t="s">
         <v>216</v>
@@ -18768,7 +18772,7 @@
         <v>288</v>
       </c>
       <c r="C306" s="6" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D306" s="1" t="s">
         <v>292</v>
@@ -18822,7 +18826,7 @@
         <v>288</v>
       </c>
       <c r="C307" s="6" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D307" s="1" t="s">
         <v>293</v>
@@ -18876,7 +18880,7 @@
         <v>288</v>
       </c>
       <c r="C308" s="6" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D308" s="1" t="s">
         <v>294</v>
@@ -18930,7 +18934,7 @@
         <v>288</v>
       </c>
       <c r="C309" s="6" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D309" s="1" t="s">
         <v>295</v>
@@ -18984,7 +18988,7 @@
         <v>288</v>
       </c>
       <c r="C310" s="6" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D310" s="1" t="s">
         <v>296</v>
@@ -19038,7 +19042,7 @@
         <v>288</v>
       </c>
       <c r="C311" s="6" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D311" s="1" t="s">
         <v>177</v>
@@ -19092,7 +19096,7 @@
         <v>288</v>
       </c>
       <c r="C312" s="6" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D312" s="1" t="s">
         <v>297</v>
@@ -19146,7 +19150,7 @@
         <v>288</v>
       </c>
       <c r="C313" s="6" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D313" s="1" t="s">
         <v>298</v>
@@ -19200,7 +19204,7 @@
         <v>288</v>
       </c>
       <c r="C314" s="6" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D314" s="1" t="s">
         <v>299</v>
@@ -19254,7 +19258,7 @@
         <v>288</v>
       </c>
       <c r="C315" s="6" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D315" s="1" t="s">
         <v>300</v>
@@ -19308,7 +19312,7 @@
         <v>288</v>
       </c>
       <c r="C316" s="6" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D316" s="1" t="s">
         <v>301</v>
@@ -19362,7 +19366,7 @@
         <v>288</v>
       </c>
       <c r="C317" s="6" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D317" s="1" t="s">
         <v>302</v>
@@ -19416,7 +19420,7 @@
         <v>288</v>
       </c>
       <c r="C318" s="6" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D318" s="1" t="s">
         <v>303</v>
@@ -19470,7 +19474,7 @@
         <v>288</v>
       </c>
       <c r="C319" s="6" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D319" s="1" t="s">
         <v>304</v>
@@ -19548,26 +19552,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>321</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
@@ -19577,7 +19581,7 @@
         <v>305</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>306</v>
@@ -21205,7 +21209,7 @@
         <v>31</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>32</v>
@@ -21259,7 +21263,7 @@
         <v>31</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>33</v>
@@ -21313,7 +21317,7 @@
         <v>31</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>34</v>
@@ -21367,7 +21371,7 @@
         <v>31</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>35</v>
@@ -21421,7 +21425,7 @@
         <v>31</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>36</v>
@@ -21475,7 +21479,7 @@
         <v>31</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>37</v>
@@ -21529,7 +21533,7 @@
         <v>31</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>38</v>
@@ -21583,7 +21587,7 @@
         <v>31</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>39</v>
@@ -21637,7 +21641,7 @@
         <v>31</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>40</v>
@@ -21691,7 +21695,7 @@
         <v>31</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>31</v>
@@ -21745,7 +21749,7 @@
         <v>31</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>41</v>
@@ -21799,7 +21803,7 @@
         <v>31</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>42</v>
@@ -21853,7 +21857,7 @@
         <v>31</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>43</v>
@@ -21907,7 +21911,7 @@
         <v>31</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>44</v>
@@ -21961,7 +21965,7 @@
         <v>31</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>45</v>
@@ -22015,7 +22019,7 @@
         <v>31</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>46</v>
@@ -22071,7 +22075,7 @@
         <v>31</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>47</v>
@@ -22127,7 +22131,7 @@
         <v>31</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>48</v>
@@ -22183,7 +22187,7 @@
         <v>31</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>49</v>
@@ -22239,7 +22243,7 @@
         <v>1</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>50</v>
@@ -22295,7 +22299,7 @@
         <v>1</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>48</v>
@@ -22349,7 +22353,7 @@
         <v>1</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>51</v>
@@ -22403,7 +22407,7 @@
         <v>1</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>25</v>
@@ -22459,7 +22463,7 @@
         <v>1</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>52</v>
@@ -22513,7 +22517,7 @@
         <v>1</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>53</v>
@@ -22567,7 +22571,7 @@
         <v>1</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>54</v>
@@ -22621,7 +22625,7 @@
         <v>1</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>55</v>
@@ -22675,7 +22679,7 @@
         <v>1</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>56</v>
@@ -22729,7 +22733,7 @@
         <v>1</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>1</v>
@@ -22783,7 +22787,7 @@
         <v>1</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>57</v>
@@ -22837,7 +22841,7 @@
         <v>1</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>58</v>
@@ -22891,7 +22895,7 @@
         <v>1</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>59</v>
@@ -22945,7 +22949,7 @@
         <v>1</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>60</v>
@@ -22999,7 +23003,7 @@
         <v>1</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>61</v>
@@ -23053,7 +23057,7 @@
         <v>1</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>62</v>
@@ -23109,7 +23113,7 @@
         <v>63</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>64</v>
@@ -23163,7 +23167,7 @@
         <v>63</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>65</v>
@@ -23217,7 +23221,7 @@
         <v>63</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>66</v>
@@ -23271,7 +23275,7 @@
         <v>63</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>58</v>
@@ -23325,7 +23329,7 @@
         <v>63</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>67</v>
@@ -23379,7 +23383,7 @@
         <v>63</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>68</v>
@@ -23433,7 +23437,7 @@
         <v>63</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>69</v>
@@ -23487,7 +23491,7 @@
         <v>63</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>70</v>
@@ -23541,7 +23545,7 @@
         <v>63</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>71</v>
@@ -23595,7 +23599,7 @@
         <v>63</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>72</v>
@@ -23649,7 +23653,7 @@
         <v>63</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>73</v>
@@ -23703,7 +23707,7 @@
         <v>63</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>74</v>
@@ -23757,7 +23761,7 @@
         <v>63</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>75</v>
@@ -23811,7 +23815,7 @@
         <v>63</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>76</v>
@@ -23865,7 +23869,7 @@
         <v>63</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>77</v>
@@ -23919,7 +23923,7 @@
         <v>63</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>78</v>
@@ -23973,7 +23977,7 @@
         <v>63</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>79</v>
@@ -24027,7 +24031,7 @@
         <v>63</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>80</v>
@@ -24081,7 +24085,7 @@
         <v>63</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>81</v>
@@ -24135,7 +24139,7 @@
         <v>63</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>82</v>
@@ -24189,7 +24193,7 @@
         <v>83</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>84</v>
@@ -24243,7 +24247,7 @@
         <v>85</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>86</v>
@@ -24297,7 +24301,7 @@
         <v>85</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>87</v>
@@ -24353,7 +24357,7 @@
         <v>85</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>88</v>
@@ -24407,7 +24411,7 @@
         <v>85</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>89</v>
@@ -24461,7 +24465,7 @@
         <v>90</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>91</v>
@@ -24515,7 +24519,7 @@
         <v>90</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>92</v>
@@ -24569,7 +24573,7 @@
         <v>90</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>93</v>
@@ -24623,7 +24627,7 @@
         <v>90</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>94</v>
@@ -24677,7 +24681,7 @@
         <v>90</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>95</v>
@@ -24731,7 +24735,7 @@
         <v>90</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>96</v>
@@ -24785,7 +24789,7 @@
         <v>90</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>97</v>
@@ -24839,7 +24843,7 @@
         <v>90</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>98</v>
@@ -24893,7 +24897,7 @@
         <v>90</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>99</v>
@@ -24947,7 +24951,7 @@
         <v>90</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>100</v>
@@ -25001,7 +25005,7 @@
         <v>90</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>101</v>
@@ -25055,7 +25059,7 @@
         <v>90</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>102</v>
@@ -25109,7 +25113,7 @@
         <v>90</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>103</v>
@@ -25163,7 +25167,7 @@
         <v>104</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>105</v>
@@ -25217,7 +25221,7 @@
         <v>104</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>106</v>
@@ -25271,7 +25275,7 @@
         <v>104</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>107</v>
@@ -25325,7 +25329,7 @@
         <v>104</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>105</v>
@@ -25379,7 +25383,7 @@
         <v>104</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>108</v>
@@ -25433,7 +25437,7 @@
         <v>104</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>1</v>
@@ -25487,7 +25491,7 @@
         <v>104</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>109</v>
@@ -25541,7 +25545,7 @@
         <v>104</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D112" s="1" t="s">
         <v>110</v>
@@ -25595,7 +25599,7 @@
         <v>104</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>111</v>
@@ -25649,7 +25653,7 @@
         <v>104</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>112</v>
@@ -25703,7 +25707,7 @@
         <v>104</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>113</v>
@@ -25757,7 +25761,7 @@
         <v>104</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>114</v>
@@ -25811,7 +25815,7 @@
         <v>104</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>115</v>
@@ -25865,7 +25869,7 @@
         <v>104</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>116</v>
@@ -25919,7 +25923,7 @@
         <v>104</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>117</v>
@@ -25973,7 +25977,7 @@
         <v>118</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>13</v>
@@ -26027,7 +26031,7 @@
         <v>118</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>119</v>
@@ -26081,7 +26085,7 @@
         <v>118</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>120</v>
@@ -26135,7 +26139,7 @@
         <v>118</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>121</v>
@@ -26189,7 +26193,7 @@
         <v>118</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>122</v>
@@ -26243,7 +26247,7 @@
         <v>118</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>123</v>
@@ -26297,7 +26301,7 @@
         <v>118</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>124</v>
@@ -26351,7 +26355,7 @@
         <v>118</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>125</v>
@@ -26405,7 +26409,7 @@
         <v>118</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D128" s="1" t="s">
         <v>126</v>
@@ -26459,7 +26463,7 @@
         <v>118</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>127</v>
@@ -26513,7 +26517,7 @@
         <v>118</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>128</v>
@@ -26567,7 +26571,7 @@
         <v>118</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>129</v>
@@ -26621,7 +26625,7 @@
         <v>118</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>130</v>
@@ -26675,7 +26679,7 @@
         <v>118</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>131</v>
@@ -26729,7 +26733,7 @@
         <v>132</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>133</v>
@@ -26785,7 +26789,7 @@
         <v>132</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>134</v>
@@ -26841,7 +26845,7 @@
         <v>132</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>135</v>
@@ -26897,7 +26901,7 @@
         <v>132</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D137" s="1" t="s">
         <v>136</v>
@@ -26953,7 +26957,7 @@
         <v>132</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>137</v>
@@ -27007,7 +27011,7 @@
         <v>132</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>138</v>
@@ -27061,7 +27065,7 @@
         <v>132</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>139</v>
@@ -27117,7 +27121,7 @@
         <v>132</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>140</v>
@@ -27173,7 +27177,7 @@
         <v>132</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>141</v>
@@ -27229,7 +27233,7 @@
         <v>132</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D143" s="1" t="s">
         <v>142</v>
@@ -27285,7 +27289,7 @@
         <v>132</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D144" s="1" t="s">
         <v>143</v>
@@ -27341,7 +27345,7 @@
         <v>132</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D145" s="1" t="s">
         <v>144</v>
@@ -27397,7 +27401,7 @@
         <v>132</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D146" s="1" t="s">
         <v>145</v>
@@ -27453,7 +27457,7 @@
         <v>132</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D147" s="1" t="s">
         <v>146</v>
@@ -27509,7 +27513,7 @@
         <v>132</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D148" s="1" t="s">
         <v>147</v>
@@ -27565,13 +27569,13 @@
         <v>132</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>148</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>348</v>
+        <v>459</v>
       </c>
       <c r="F149" s="2">
         <v>-52.9</v>
@@ -27621,7 +27625,7 @@
         <v>132</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D150" s="1" t="s">
         <v>149</v>
@@ -27677,7 +27681,7 @@
         <v>132</v>
       </c>
       <c r="C151" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D151" s="1" t="s">
         <v>150</v>
@@ -27733,7 +27737,7 @@
         <v>132</v>
       </c>
       <c r="C152" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D152" s="1" t="s">
         <v>151</v>
@@ -27789,7 +27793,7 @@
         <v>132</v>
       </c>
       <c r="C153" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D153" s="1" t="s">
         <v>152</v>
@@ -27843,7 +27847,7 @@
         <v>132</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D154" s="1" t="s">
         <v>153</v>
@@ -27899,7 +27903,7 @@
         <v>132</v>
       </c>
       <c r="C155" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D155" s="1" t="s">
         <v>154</v>
@@ -27955,7 +27959,7 @@
         <v>132</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D156" s="1" t="s">
         <v>155</v>
@@ -28011,7 +28015,7 @@
         <v>55</v>
       </c>
       <c r="C157" s="6" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D157" s="1" t="s">
         <v>156</v>
@@ -28065,7 +28069,7 @@
         <v>55</v>
       </c>
       <c r="C158" s="6" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D158" s="1" t="s">
         <v>157</v>
@@ -28119,7 +28123,7 @@
         <v>158</v>
       </c>
       <c r="C159" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D159" s="1" t="s">
         <v>159</v>
@@ -28173,7 +28177,7 @@
         <v>158</v>
       </c>
       <c r="C160" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D160" s="1" t="s">
         <v>36</v>
@@ -28227,7 +28231,7 @@
         <v>158</v>
       </c>
       <c r="C161" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D161" s="1" t="s">
         <v>160</v>
@@ -28281,7 +28285,7 @@
         <v>158</v>
       </c>
       <c r="C162" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D162" s="1" t="s">
         <v>161</v>
@@ -28335,7 +28339,7 @@
         <v>158</v>
       </c>
       <c r="C163" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D163" s="1" t="s">
         <v>71</v>
@@ -28389,7 +28393,7 @@
         <v>158</v>
       </c>
       <c r="C164" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D164" s="1" t="s">
         <v>162</v>
@@ -28443,7 +28447,7 @@
         <v>158</v>
       </c>
       <c r="C165" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D165" s="1" t="s">
         <v>163</v>
@@ -28497,7 +28501,7 @@
         <v>158</v>
       </c>
       <c r="C166" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D166" s="1" t="s">
         <v>164</v>
@@ -28551,7 +28555,7 @@
         <v>158</v>
       </c>
       <c r="C167" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D167" s="1" t="s">
         <v>165</v>
@@ -28605,7 +28609,7 @@
         <v>158</v>
       </c>
       <c r="C168" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D168" s="1" t="s">
         <v>166</v>
@@ -28659,7 +28663,7 @@
         <v>158</v>
       </c>
       <c r="C169" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D169" s="1" t="s">
         <v>167</v>
@@ -28713,7 +28717,7 @@
         <v>158</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D170" s="1" t="s">
         <v>168</v>
@@ -28767,7 +28771,7 @@
         <v>158</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D171" s="1" t="s">
         <v>169</v>
@@ -28821,7 +28825,7 @@
         <v>158</v>
       </c>
       <c r="C172" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D172" s="1" t="s">
         <v>170</v>
@@ -28875,7 +28879,7 @@
         <v>158</v>
       </c>
       <c r="C173" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D173" s="1" t="s">
         <v>171</v>
@@ -28929,7 +28933,7 @@
         <v>158</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D174" s="1" t="s">
         <v>172</v>
@@ -28983,7 +28987,7 @@
         <v>158</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D175" s="1" t="s">
         <v>173</v>
@@ -29037,7 +29041,7 @@
         <v>158</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D176" s="1" t="s">
         <v>174</v>
@@ -29091,7 +29095,7 @@
         <v>175</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D177" s="1" t="s">
         <v>176</v>
@@ -29145,7 +29149,7 @@
         <v>175</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D178" s="1" t="s">
         <v>177</v>
@@ -29199,7 +29203,7 @@
         <v>175</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D179" s="1" t="s">
         <v>178</v>
@@ -29253,7 +29257,7 @@
         <v>175</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D180" s="1" t="s">
         <v>179</v>
@@ -29307,7 +29311,7 @@
         <v>175</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D181" s="1" t="s">
         <v>180</v>
@@ -29363,7 +29367,7 @@
         <v>175</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D182" s="1" t="s">
         <v>181</v>
@@ -29417,7 +29421,7 @@
         <v>175</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D183" s="1" t="s">
         <v>182</v>
@@ -29471,7 +29475,7 @@
         <v>175</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D184" s="1" t="s">
         <v>183</v>
@@ -29525,7 +29529,7 @@
         <v>175</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D185" s="1" t="s">
         <v>184</v>
@@ -29579,7 +29583,7 @@
         <v>175</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D186" s="1" t="s">
         <v>185</v>
@@ -29633,7 +29637,7 @@
         <v>175</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D187" s="1" t="s">
         <v>186</v>
@@ -29687,7 +29691,7 @@
         <v>175</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D188" s="1" t="s">
         <v>187</v>
@@ -29741,7 +29745,7 @@
         <v>175</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D189" s="1" t="s">
         <v>188</v>
@@ -29795,7 +29799,7 @@
         <v>175</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D190" s="1" t="s">
         <v>189</v>
@@ -29849,7 +29853,7 @@
         <v>190</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D191" s="1" t="s">
         <v>191</v>
@@ -29903,7 +29907,7 @@
         <v>190</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D192" s="1" t="s">
         <v>192</v>
@@ -29957,7 +29961,7 @@
         <v>190</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D193" s="1" t="s">
         <v>193</v>
@@ -30011,7 +30015,7 @@
         <v>190</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D194" s="1" t="s">
         <v>194</v>
@@ -30065,7 +30069,7 @@
         <v>190</v>
       </c>
       <c r="C195" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D195" s="1" t="s">
         <v>195</v>
@@ -30119,7 +30123,7 @@
         <v>190</v>
       </c>
       <c r="C196" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D196" s="1" t="s">
         <v>196</v>
@@ -30173,7 +30177,7 @@
         <v>190</v>
       </c>
       <c r="C197" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D197" s="1" t="s">
         <v>197</v>
@@ -30227,7 +30231,7 @@
         <v>190</v>
       </c>
       <c r="C198" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D198" s="1" t="s">
         <v>198</v>
@@ -30281,7 +30285,7 @@
         <v>190</v>
       </c>
       <c r="C199" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D199" s="1" t="s">
         <v>199</v>
@@ -30335,7 +30339,7 @@
         <v>190</v>
       </c>
       <c r="C200" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D200" s="1" t="s">
         <v>200</v>
@@ -30389,7 +30393,7 @@
         <v>190</v>
       </c>
       <c r="C201" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D201" s="1" t="s">
         <v>190</v>
@@ -30443,7 +30447,7 @@
         <v>190</v>
       </c>
       <c r="C202" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D202" s="1" t="s">
         <v>201</v>
@@ -30497,7 +30501,7 @@
         <v>190</v>
       </c>
       <c r="C203" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D203" s="1" t="s">
         <v>202</v>
@@ -30551,7 +30555,7 @@
         <v>203</v>
       </c>
       <c r="C204" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D204" s="1" t="s">
         <v>204</v>
@@ -30605,7 +30609,7 @@
         <v>203</v>
       </c>
       <c r="C205" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D205" s="1" t="s">
         <v>205</v>
@@ -30661,7 +30665,7 @@
         <v>203</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D206" s="1" t="s">
         <v>206</v>
@@ -30715,7 +30719,7 @@
         <v>203</v>
       </c>
       <c r="C207" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D207" s="1" t="s">
         <v>207</v>
@@ -30769,13 +30773,13 @@
         <v>203</v>
       </c>
       <c r="C208" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D208" s="1" t="s">
         <v>55</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F208" s="2">
         <v>-48.5</v>
@@ -30825,7 +30829,7 @@
         <v>203</v>
       </c>
       <c r="C209" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D209" s="1" t="s">
         <v>208</v>
@@ -30879,7 +30883,7 @@
         <v>203</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D210" s="1" t="s">
         <v>209</v>
@@ -30933,7 +30937,7 @@
         <v>203</v>
       </c>
       <c r="C211" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D211" s="1" t="s">
         <v>210</v>
@@ -30989,7 +30993,7 @@
         <v>203</v>
       </c>
       <c r="C212" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D212" s="1" t="s">
         <v>211</v>
@@ -31045,7 +31049,7 @@
         <v>203</v>
       </c>
       <c r="C213" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D213" s="1" t="s">
         <v>212</v>
@@ -31101,7 +31105,7 @@
         <v>203</v>
       </c>
       <c r="C214" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D214" s="1" t="s">
         <v>190</v>
@@ -31155,7 +31159,7 @@
         <v>203</v>
       </c>
       <c r="C215" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D215" s="1" t="s">
         <v>213</v>
@@ -31211,7 +31215,7 @@
         <v>203</v>
       </c>
       <c r="C216" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D216" s="1" t="s">
         <v>214</v>
@@ -31265,7 +31269,7 @@
         <v>215</v>
       </c>
       <c r="C217" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D217" s="1" t="s">
         <v>216</v>
@@ -31319,7 +31323,7 @@
         <v>215</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D218" s="1" t="s">
         <v>217</v>
@@ -31373,7 +31377,7 @@
         <v>215</v>
       </c>
       <c r="C219" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D219" s="1" t="s">
         <v>218</v>
@@ -31427,7 +31431,7 @@
         <v>215</v>
       </c>
       <c r="C220" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D220" s="1" t="s">
         <v>219</v>
@@ -31481,7 +31485,7 @@
         <v>215</v>
       </c>
       <c r="C221" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D221" s="1" t="s">
         <v>126</v>
@@ -31537,7 +31541,7 @@
         <v>215</v>
       </c>
       <c r="C222" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D222" s="1" t="s">
         <v>220</v>
@@ -31591,7 +31595,7 @@
         <v>215</v>
       </c>
       <c r="C223" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D223" s="1" t="s">
         <v>221</v>
@@ -31647,7 +31651,7 @@
         <v>215</v>
       </c>
       <c r="C224" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D224" s="1" t="s">
         <v>222</v>
@@ -31701,7 +31705,7 @@
         <v>215</v>
       </c>
       <c r="C225" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D225" s="1" t="s">
         <v>223</v>
@@ -31755,7 +31759,7 @@
         <v>215</v>
       </c>
       <c r="C226" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D226" s="1" t="s">
         <v>66</v>
@@ -31811,7 +31815,7 @@
         <v>215</v>
       </c>
       <c r="C227" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D227" s="1" t="s">
         <v>37</v>
@@ -31865,7 +31869,7 @@
         <v>215</v>
       </c>
       <c r="C228" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D228" s="1" t="s">
         <v>224</v>
@@ -31921,7 +31925,7 @@
         <v>215</v>
       </c>
       <c r="C229" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D229" s="1" t="s">
         <v>225</v>
@@ -31975,7 +31979,7 @@
         <v>215</v>
       </c>
       <c r="C230" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D230" s="1" t="s">
         <v>226</v>
@@ -32029,7 +32033,7 @@
         <v>215</v>
       </c>
       <c r="C231" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D231" s="1" t="s">
         <v>227</v>
@@ -32083,7 +32087,7 @@
         <v>215</v>
       </c>
       <c r="C232" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D232" s="1" t="s">
         <v>228</v>
@@ -32137,7 +32141,7 @@
         <v>215</v>
       </c>
       <c r="C233" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D233" s="1" t="s">
         <v>229</v>
@@ -32191,7 +32195,7 @@
         <v>215</v>
       </c>
       <c r="C234" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D234" s="1" t="s">
         <v>230</v>
@@ -32245,7 +32249,7 @@
         <v>215</v>
       </c>
       <c r="C235" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D235" s="1" t="s">
         <v>231</v>
@@ -32299,7 +32303,7 @@
         <v>215</v>
       </c>
       <c r="C236" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D236" s="1" t="s">
         <v>232</v>
@@ -32355,7 +32359,7 @@
         <v>215</v>
       </c>
       <c r="C237" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D237" s="1" t="s">
         <v>8</v>
@@ -32409,7 +32413,7 @@
         <v>233</v>
       </c>
       <c r="C238" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D238" s="1" t="s">
         <v>132</v>
@@ -32465,7 +32469,7 @@
         <v>233</v>
       </c>
       <c r="C239" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D239" s="1" t="s">
         <v>29</v>
@@ -32521,7 +32525,7 @@
         <v>233</v>
       </c>
       <c r="C240" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D240" s="1" t="s">
         <v>234</v>
@@ -32577,7 +32581,7 @@
         <v>233</v>
       </c>
       <c r="C241" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D241" s="1" t="s">
         <v>235</v>
@@ -32633,7 +32637,7 @@
         <v>233</v>
       </c>
       <c r="C242" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D242" s="1" t="s">
         <v>236</v>
@@ -32689,7 +32693,7 @@
         <v>233</v>
       </c>
       <c r="C243" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D243" s="1" t="s">
         <v>237</v>
@@ -32745,7 +32749,7 @@
         <v>233</v>
       </c>
       <c r="C244" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D244" s="1" t="s">
         <v>238</v>
@@ -32801,7 +32805,7 @@
         <v>233</v>
       </c>
       <c r="C245" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D245" s="1" t="s">
         <v>136</v>
@@ -32857,7 +32861,7 @@
         <v>233</v>
       </c>
       <c r="C246" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D246" s="1" t="s">
         <v>239</v>
@@ -32913,7 +32917,7 @@
         <v>233</v>
       </c>
       <c r="C247" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D247" s="1" t="s">
         <v>240</v>
@@ -32969,7 +32973,7 @@
         <v>233</v>
       </c>
       <c r="C248" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D248" s="1" t="s">
         <v>241</v>
@@ -33025,7 +33029,7 @@
         <v>233</v>
       </c>
       <c r="C249" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D249" s="1" t="s">
         <v>242</v>
@@ -33081,7 +33085,7 @@
         <v>233</v>
       </c>
       <c r="C250" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D250" s="1" t="s">
         <v>243</v>
@@ -33137,7 +33141,7 @@
         <v>233</v>
       </c>
       <c r="C251" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D251" s="1" t="s">
         <v>244</v>
@@ -33193,7 +33197,7 @@
         <v>233</v>
       </c>
       <c r="C252" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D252" s="1" t="s">
         <v>245</v>
@@ -33249,7 +33253,7 @@
         <v>233</v>
       </c>
       <c r="C253" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D253" s="1" t="s">
         <v>246</v>
@@ -33305,7 +33309,7 @@
         <v>233</v>
       </c>
       <c r="C254" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D254" s="1" t="s">
         <v>155</v>
@@ -33361,7 +33365,7 @@
         <v>233</v>
       </c>
       <c r="C255" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D255" s="1" t="s">
         <v>247</v>
@@ -33417,7 +33421,7 @@
         <v>248</v>
       </c>
       <c r="C256" s="6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D256" s="1" t="s">
         <v>249</v>
@@ -33471,7 +33475,7 @@
         <v>248</v>
       </c>
       <c r="C257" s="6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D257" s="1" t="s">
         <v>13</v>
@@ -33525,7 +33529,7 @@
         <v>248</v>
       </c>
       <c r="C258" s="6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D258" s="1" t="s">
         <v>250</v>
@@ -33579,7 +33583,7 @@
         <v>248</v>
       </c>
       <c r="C259" s="6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D259" s="1" t="s">
         <v>248</v>
@@ -33635,7 +33639,7 @@
         <v>248</v>
       </c>
       <c r="C260" s="6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D260" s="1" t="s">
         <v>251</v>
@@ -33689,7 +33693,7 @@
         <v>248</v>
       </c>
       <c r="C261" s="6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D261" s="1" t="s">
         <v>252</v>
@@ -33743,7 +33747,7 @@
         <v>253</v>
       </c>
       <c r="C262" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D262" s="1" t="s">
         <v>254</v>
@@ -33797,7 +33801,7 @@
         <v>253</v>
       </c>
       <c r="C263" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D263" s="1" t="s">
         <v>255</v>
@@ -33851,7 +33855,7 @@
         <v>253</v>
       </c>
       <c r="C264" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D264" s="1" t="s">
         <v>256</v>
@@ -33905,7 +33909,7 @@
         <v>253</v>
       </c>
       <c r="C265" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D265" s="1" t="s">
         <v>257</v>
@@ -33961,7 +33965,7 @@
         <v>253</v>
       </c>
       <c r="C266" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D266" s="1" t="s">
         <v>258</v>
@@ -34015,7 +34019,7 @@
         <v>253</v>
       </c>
       <c r="C267" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D267" s="1" t="s">
         <v>259</v>
@@ -34069,7 +34073,7 @@
         <v>253</v>
       </c>
       <c r="C268" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D268" s="1" t="s">
         <v>77</v>
@@ -34123,7 +34127,7 @@
         <v>253</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D269" s="1" t="s">
         <v>260</v>
@@ -34177,7 +34181,7 @@
         <v>253</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D270" s="1" t="s">
         <v>261</v>
@@ -34231,7 +34235,7 @@
         <v>253</v>
       </c>
       <c r="C271" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D271" s="1" t="s">
         <v>262</v>
@@ -34285,7 +34289,7 @@
         <v>253</v>
       </c>
       <c r="C272" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D272" s="1" t="s">
         <v>263</v>
@@ -34341,7 +34345,7 @@
         <v>253</v>
       </c>
       <c r="C273" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D273" s="1" t="s">
         <v>264</v>
@@ -34395,7 +34399,7 @@
         <v>253</v>
       </c>
       <c r="C274" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D274" s="1" t="s">
         <v>265</v>
@@ -34449,7 +34453,7 @@
         <v>253</v>
       </c>
       <c r="C275" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D275" s="1" t="s">
         <v>266</v>
@@ -34503,7 +34507,7 @@
         <v>253</v>
       </c>
       <c r="C276" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D276" s="1" t="s">
         <v>267</v>
@@ -34559,7 +34563,7 @@
         <v>253</v>
       </c>
       <c r="C277" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D277" s="1" t="s">
         <v>68</v>
@@ -34613,7 +34617,7 @@
         <v>93</v>
       </c>
       <c r="C278" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D278" s="1" t="s">
         <v>268</v>
@@ -34669,7 +34673,7 @@
         <v>93</v>
       </c>
       <c r="C279" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D279" s="1" t="s">
         <v>269</v>
@@ -34723,7 +34727,7 @@
         <v>93</v>
       </c>
       <c r="C280" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D280" s="1" t="s">
         <v>270</v>
@@ -34777,7 +34781,7 @@
         <v>93</v>
       </c>
       <c r="C281" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D281" s="1" t="s">
         <v>50</v>
@@ -34831,7 +34835,7 @@
         <v>93</v>
       </c>
       <c r="C282" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D282" s="1" t="s">
         <v>271</v>
@@ -34885,7 +34889,7 @@
         <v>93</v>
       </c>
       <c r="C283" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D283" s="1" t="s">
         <v>148</v>
@@ -34941,7 +34945,7 @@
         <v>93</v>
       </c>
       <c r="C284" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D284" s="1" t="s">
         <v>149</v>
@@ -34995,7 +34999,7 @@
         <v>93</v>
       </c>
       <c r="C285" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D285" s="1" t="s">
         <v>272</v>
@@ -35049,7 +35053,7 @@
         <v>93</v>
       </c>
       <c r="C286" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D286" s="1" t="s">
         <v>273</v>
@@ -35103,7 +35107,7 @@
         <v>93</v>
       </c>
       <c r="C287" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D287" s="1" t="s">
         <v>274</v>
@@ -35159,7 +35163,7 @@
         <v>93</v>
       </c>
       <c r="C288" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D288" s="1" t="s">
         <v>275</v>
@@ -35215,7 +35219,7 @@
         <v>93</v>
       </c>
       <c r="C289" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D289" s="1" t="s">
         <v>276</v>
@@ -35269,7 +35273,7 @@
         <v>93</v>
       </c>
       <c r="C290" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D290" s="1" t="s">
         <v>277</v>
@@ -35325,7 +35329,7 @@
         <v>93</v>
       </c>
       <c r="C291" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D291" s="1" t="s">
         <v>278</v>
@@ -35381,7 +35385,7 @@
         <v>93</v>
       </c>
       <c r="C292" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D292" s="1" t="s">
         <v>279</v>
@@ -35437,7 +35441,7 @@
         <v>93</v>
       </c>
       <c r="C293" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D293" s="1" t="s">
         <v>280</v>
@@ -35493,7 +35497,7 @@
         <v>93</v>
       </c>
       <c r="C294" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D294" s="1" t="s">
         <v>281</v>
@@ -35549,7 +35553,7 @@
         <v>93</v>
       </c>
       <c r="C295" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D295" s="1" t="s">
         <v>282</v>
@@ -35605,7 +35609,7 @@
         <v>93</v>
       </c>
       <c r="C296" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D296" s="1" t="s">
         <v>283</v>
@@ -35661,7 +35665,7 @@
         <v>93</v>
       </c>
       <c r="C297" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D297" s="1" t="s">
         <v>284</v>
@@ -35715,7 +35719,7 @@
         <v>93</v>
       </c>
       <c r="C298" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D298" s="1" t="s">
         <v>285</v>
@@ -35771,7 +35775,7 @@
         <v>93</v>
       </c>
       <c r="C299" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D299" s="1" t="s">
         <v>286</v>
@@ -35827,7 +35831,7 @@
         <v>93</v>
       </c>
       <c r="C300" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D300" s="1" t="s">
         <v>213</v>
@@ -35883,13 +35887,13 @@
         <v>93</v>
       </c>
       <c r="C301" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D301" s="1" t="s">
         <v>287</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="F301" s="2">
         <v>-38</v>
@@ -35939,7 +35943,7 @@
         <v>288</v>
       </c>
       <c r="C302" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D302" s="1" t="s">
         <v>289</v>
@@ -35993,7 +35997,7 @@
         <v>288</v>
       </c>
       <c r="C303" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D303" s="1" t="s">
         <v>290</v>
@@ -36047,7 +36051,7 @@
         <v>288</v>
       </c>
       <c r="C304" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D304" s="1" t="s">
         <v>291</v>
@@ -36101,7 +36105,7 @@
         <v>288</v>
       </c>
       <c r="C305" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D305" s="1" t="s">
         <v>216</v>
@@ -36155,7 +36159,7 @@
         <v>288</v>
       </c>
       <c r="C306" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D306" s="1" t="s">
         <v>292</v>
@@ -36209,7 +36213,7 @@
         <v>288</v>
       </c>
       <c r="C307" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D307" s="1" t="s">
         <v>293</v>
@@ -36263,7 +36267,7 @@
         <v>288</v>
       </c>
       <c r="C308" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D308" s="1" t="s">
         <v>294</v>
@@ -36317,7 +36321,7 @@
         <v>288</v>
       </c>
       <c r="C309" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D309" s="1" t="s">
         <v>295</v>
@@ -36371,7 +36375,7 @@
         <v>288</v>
       </c>
       <c r="C310" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D310" s="1" t="s">
         <v>296</v>
@@ -36425,7 +36429,7 @@
         <v>288</v>
       </c>
       <c r="C311" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D311" s="1" t="s">
         <v>177</v>
@@ -36479,7 +36483,7 @@
         <v>288</v>
       </c>
       <c r="C312" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D312" s="1" t="s">
         <v>297</v>
@@ -36533,7 +36537,7 @@
         <v>288</v>
       </c>
       <c r="C313" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D313" s="1" t="s">
         <v>298</v>
@@ -36587,7 +36591,7 @@
         <v>288</v>
       </c>
       <c r="C314" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D314" s="1" t="s">
         <v>299</v>
@@ -36641,7 +36645,7 @@
         <v>288</v>
       </c>
       <c r="C315" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D315" s="1" t="s">
         <v>300</v>
@@ -36695,7 +36699,7 @@
         <v>288</v>
       </c>
       <c r="C316" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D316" s="1" t="s">
         <v>301</v>
@@ -36749,7 +36753,7 @@
         <v>288</v>
       </c>
       <c r="C317" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D317" s="1" t="s">
         <v>302</v>
@@ -36803,7 +36807,7 @@
         <v>288</v>
       </c>
       <c r="C318" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D318" s="1" t="s">
         <v>303</v>
@@ -36857,7 +36861,7 @@
         <v>288</v>
       </c>
       <c r="C319" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D319" s="1" t="s">
         <v>304</v>
@@ -36932,26 +36936,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11"/>
-      <c r="R1" s="11"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
@@ -36961,7 +36965,7 @@
         <v>305</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>306</v>
@@ -38589,7 +38593,7 @@
         <v>31</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>32</v>
@@ -38643,7 +38647,7 @@
         <v>31</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>33</v>
@@ -38697,7 +38701,7 @@
         <v>31</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>34</v>
@@ -38751,7 +38755,7 @@
         <v>31</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>35</v>
@@ -38805,7 +38809,7 @@
         <v>31</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>36</v>
@@ -38859,7 +38863,7 @@
         <v>31</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>37</v>
@@ -38913,7 +38917,7 @@
         <v>31</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>38</v>
@@ -38967,7 +38971,7 @@
         <v>31</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>39</v>
@@ -39021,7 +39025,7 @@
         <v>31</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>40</v>
@@ -39075,7 +39079,7 @@
         <v>31</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>31</v>
@@ -39129,7 +39133,7 @@
         <v>31</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>41</v>
@@ -39183,7 +39187,7 @@
         <v>31</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>42</v>
@@ -39237,7 +39241,7 @@
         <v>31</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>43</v>
@@ -39291,7 +39295,7 @@
         <v>31</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>44</v>
@@ -39345,7 +39349,7 @@
         <v>31</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>45</v>
@@ -39399,7 +39403,7 @@
         <v>31</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>46</v>
@@ -39455,7 +39459,7 @@
         <v>31</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>47</v>
@@ -39511,7 +39515,7 @@
         <v>31</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>48</v>
@@ -39567,7 +39571,7 @@
         <v>31</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>49</v>
@@ -39623,7 +39627,7 @@
         <v>1</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>50</v>
@@ -39679,7 +39683,7 @@
         <v>1</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>48</v>
@@ -39733,7 +39737,7 @@
         <v>1</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>51</v>
@@ -39787,7 +39791,7 @@
         <v>1</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>25</v>
@@ -39843,7 +39847,7 @@
         <v>1</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>52</v>
@@ -39897,7 +39901,7 @@
         <v>1</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>53</v>
@@ -39951,7 +39955,7 @@
         <v>1</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>54</v>
@@ -40005,7 +40009,7 @@
         <v>1</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>55</v>
@@ -40059,7 +40063,7 @@
         <v>1</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>56</v>
@@ -40113,7 +40117,7 @@
         <v>1</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>1</v>
@@ -40167,7 +40171,7 @@
         <v>1</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>57</v>
@@ -40221,7 +40225,7 @@
         <v>1</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>58</v>
@@ -40275,7 +40279,7 @@
         <v>1</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>59</v>
@@ -40329,7 +40333,7 @@
         <v>1</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>60</v>
@@ -40383,7 +40387,7 @@
         <v>1</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>61</v>
@@ -40437,7 +40441,7 @@
         <v>1</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>62</v>
@@ -40493,7 +40497,7 @@
         <v>63</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>64</v>
@@ -40547,7 +40551,7 @@
         <v>63</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>65</v>
@@ -40601,7 +40605,7 @@
         <v>63</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>66</v>
@@ -40655,7 +40659,7 @@
         <v>63</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>58</v>
@@ -40709,7 +40713,7 @@
         <v>63</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>67</v>
@@ -40763,7 +40767,7 @@
         <v>63</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>68</v>
@@ -40817,7 +40821,7 @@
         <v>63</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>69</v>
@@ -40871,7 +40875,7 @@
         <v>63</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>70</v>
@@ -40925,7 +40929,7 @@
         <v>63</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>71</v>
@@ -40979,7 +40983,7 @@
         <v>63</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>72</v>
@@ -41033,7 +41037,7 @@
         <v>63</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>73</v>
@@ -41087,7 +41091,7 @@
         <v>63</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>74</v>
@@ -41141,7 +41145,7 @@
         <v>63</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>75</v>
@@ -41195,7 +41199,7 @@
         <v>63</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>76</v>
@@ -41249,7 +41253,7 @@
         <v>63</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>77</v>
@@ -41303,7 +41307,7 @@
         <v>63</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>78</v>
@@ -41357,7 +41361,7 @@
         <v>63</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>79</v>
@@ -41411,7 +41415,7 @@
         <v>63</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>80</v>
@@ -41465,7 +41469,7 @@
         <v>63</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>81</v>
@@ -41519,7 +41523,7 @@
         <v>63</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>82</v>
@@ -41573,7 +41577,7 @@
         <v>83</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>84</v>
@@ -41627,7 +41631,7 @@
         <v>85</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>86</v>
@@ -41681,7 +41685,7 @@
         <v>85</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>87</v>
@@ -41737,7 +41741,7 @@
         <v>85</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>88</v>
@@ -41791,7 +41795,7 @@
         <v>85</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>89</v>
@@ -41845,7 +41849,7 @@
         <v>90</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>91</v>
@@ -41899,7 +41903,7 @@
         <v>90</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>92</v>
@@ -41953,7 +41957,7 @@
         <v>90</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>93</v>
@@ -42007,7 +42011,7 @@
         <v>90</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>94</v>
@@ -42061,7 +42065,7 @@
         <v>90</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>95</v>
@@ -42115,7 +42119,7 @@
         <v>90</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>96</v>
@@ -42169,7 +42173,7 @@
         <v>90</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>97</v>
@@ -42223,7 +42227,7 @@
         <v>90</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>98</v>
@@ -42277,7 +42281,7 @@
         <v>90</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>99</v>
@@ -42331,7 +42335,7 @@
         <v>90</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>100</v>
@@ -42385,7 +42389,7 @@
         <v>90</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>101</v>
@@ -42439,7 +42443,7 @@
         <v>90</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>102</v>
@@ -42493,7 +42497,7 @@
         <v>90</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>103</v>
@@ -42547,7 +42551,7 @@
         <v>104</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>105</v>
@@ -42601,7 +42605,7 @@
         <v>104</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>106</v>
@@ -42655,7 +42659,7 @@
         <v>104</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>107</v>
@@ -42709,7 +42713,7 @@
         <v>104</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>105</v>
@@ -42763,7 +42767,7 @@
         <v>104</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>108</v>
@@ -42817,7 +42821,7 @@
         <v>104</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>1</v>
@@ -42871,7 +42875,7 @@
         <v>104</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>109</v>
@@ -42925,7 +42929,7 @@
         <v>104</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D112" s="1" t="s">
         <v>110</v>
@@ -42979,7 +42983,7 @@
         <v>104</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>111</v>
@@ -43033,7 +43037,7 @@
         <v>104</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>112</v>
@@ -43087,7 +43091,7 @@
         <v>104</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>113</v>
@@ -43141,7 +43145,7 @@
         <v>104</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>114</v>
@@ -43195,7 +43199,7 @@
         <v>104</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>115</v>
@@ -43249,7 +43253,7 @@
         <v>104</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>116</v>
@@ -43303,7 +43307,7 @@
         <v>104</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>117</v>
@@ -43357,7 +43361,7 @@
         <v>118</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>13</v>
@@ -43411,7 +43415,7 @@
         <v>118</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>119</v>
@@ -43465,7 +43469,7 @@
         <v>118</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>120</v>
@@ -43519,7 +43523,7 @@
         <v>118</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>121</v>
@@ -43573,7 +43577,7 @@
         <v>118</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>122</v>
@@ -43627,7 +43631,7 @@
         <v>118</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>123</v>
@@ -43681,7 +43685,7 @@
         <v>118</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>124</v>
@@ -43735,7 +43739,7 @@
         <v>118</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>125</v>
@@ -43789,7 +43793,7 @@
         <v>118</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D128" s="1" t="s">
         <v>126</v>
@@ -43843,7 +43847,7 @@
         <v>118</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>127</v>
@@ -43897,7 +43901,7 @@
         <v>118</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>128</v>
@@ -43951,7 +43955,7 @@
         <v>118</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>129</v>
@@ -44005,7 +44009,7 @@
         <v>118</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>130</v>
@@ -44059,7 +44063,7 @@
         <v>118</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>131</v>
@@ -44113,7 +44117,7 @@
         <v>132</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>133</v>
@@ -44169,7 +44173,7 @@
         <v>132</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>134</v>
@@ -44225,7 +44229,7 @@
         <v>132</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>135</v>
@@ -44281,7 +44285,7 @@
         <v>132</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D137" s="1" t="s">
         <v>136</v>
@@ -44337,7 +44341,7 @@
         <v>132</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>137</v>
@@ -44391,7 +44395,7 @@
         <v>132</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>138</v>
@@ -44445,7 +44449,7 @@
         <v>132</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>139</v>
@@ -44501,7 +44505,7 @@
         <v>132</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>140</v>
@@ -44557,7 +44561,7 @@
         <v>132</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>141</v>
@@ -44613,7 +44617,7 @@
         <v>132</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D143" s="1" t="s">
         <v>142</v>
@@ -44669,7 +44673,7 @@
         <v>132</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D144" s="1" t="s">
         <v>143</v>
@@ -44725,7 +44729,7 @@
         <v>132</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D145" s="1" t="s">
         <v>144</v>
@@ -44781,7 +44785,7 @@
         <v>132</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D146" s="1" t="s">
         <v>145</v>
@@ -44837,7 +44841,7 @@
         <v>132</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D147" s="1" t="s">
         <v>146</v>
@@ -44893,7 +44897,7 @@
         <v>132</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D148" s="1" t="s">
         <v>147</v>
@@ -44949,13 +44953,13 @@
         <v>132</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>148</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>348</v>
+        <v>459</v>
       </c>
       <c r="F149" s="2">
         <v>0.6</v>
@@ -45005,7 +45009,7 @@
         <v>132</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D150" s="1" t="s">
         <v>149</v>
@@ -45061,7 +45065,7 @@
         <v>132</v>
       </c>
       <c r="C151" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D151" s="1" t="s">
         <v>150</v>
@@ -45117,7 +45121,7 @@
         <v>132</v>
       </c>
       <c r="C152" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D152" s="1" t="s">
         <v>151</v>
@@ -45173,7 +45177,7 @@
         <v>132</v>
       </c>
       <c r="C153" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D153" s="1" t="s">
         <v>152</v>
@@ -45227,7 +45231,7 @@
         <v>132</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D154" s="1" t="s">
         <v>153</v>
@@ -45283,7 +45287,7 @@
         <v>132</v>
       </c>
       <c r="C155" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D155" s="1" t="s">
         <v>154</v>
@@ -45339,7 +45343,7 @@
         <v>132</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D156" s="1" t="s">
         <v>155</v>
@@ -45395,7 +45399,7 @@
         <v>55</v>
       </c>
       <c r="C157" s="6" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D157" s="1" t="s">
         <v>156</v>
@@ -45449,7 +45453,7 @@
         <v>55</v>
       </c>
       <c r="C158" s="6" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D158" s="1" t="s">
         <v>157</v>
@@ -45503,7 +45507,7 @@
         <v>158</v>
       </c>
       <c r="C159" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D159" s="1" t="s">
         <v>159</v>
@@ -45557,7 +45561,7 @@
         <v>158</v>
       </c>
       <c r="C160" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D160" s="1" t="s">
         <v>36</v>
@@ -45611,7 +45615,7 @@
         <v>158</v>
       </c>
       <c r="C161" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D161" s="1" t="s">
         <v>160</v>
@@ -45665,7 +45669,7 @@
         <v>158</v>
       </c>
       <c r="C162" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D162" s="1" t="s">
         <v>161</v>
@@ -45719,7 +45723,7 @@
         <v>158</v>
       </c>
       <c r="C163" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D163" s="1" t="s">
         <v>71</v>
@@ -45773,7 +45777,7 @@
         <v>158</v>
       </c>
       <c r="C164" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D164" s="1" t="s">
         <v>162</v>
@@ -45827,7 +45831,7 @@
         <v>158</v>
       </c>
       <c r="C165" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D165" s="1" t="s">
         <v>163</v>
@@ -45881,7 +45885,7 @@
         <v>158</v>
       </c>
       <c r="C166" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D166" s="1" t="s">
         <v>164</v>
@@ -45935,7 +45939,7 @@
         <v>158</v>
       </c>
       <c r="C167" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D167" s="1" t="s">
         <v>165</v>
@@ -45989,7 +45993,7 @@
         <v>158</v>
       </c>
       <c r="C168" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D168" s="1" t="s">
         <v>166</v>
@@ -46043,7 +46047,7 @@
         <v>158</v>
       </c>
       <c r="C169" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D169" s="1" t="s">
         <v>167</v>
@@ -46097,7 +46101,7 @@
         <v>158</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D170" s="1" t="s">
         <v>168</v>
@@ -46151,7 +46155,7 @@
         <v>158</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D171" s="1" t="s">
         <v>169</v>
@@ -46205,7 +46209,7 @@
         <v>158</v>
       </c>
       <c r="C172" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D172" s="1" t="s">
         <v>170</v>
@@ -46259,7 +46263,7 @@
         <v>158</v>
       </c>
       <c r="C173" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D173" s="1" t="s">
         <v>171</v>
@@ -46313,7 +46317,7 @@
         <v>158</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D174" s="1" t="s">
         <v>172</v>
@@ -46367,7 +46371,7 @@
         <v>158</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D175" s="1" t="s">
         <v>173</v>
@@ -46421,7 +46425,7 @@
         <v>158</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D176" s="1" t="s">
         <v>174</v>
@@ -46475,7 +46479,7 @@
         <v>175</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D177" s="1" t="s">
         <v>176</v>
@@ -46529,7 +46533,7 @@
         <v>175</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D178" s="1" t="s">
         <v>177</v>
@@ -46583,7 +46587,7 @@
         <v>175</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D179" s="1" t="s">
         <v>178</v>
@@ -46637,7 +46641,7 @@
         <v>175</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D180" s="1" t="s">
         <v>179</v>
@@ -46691,7 +46695,7 @@
         <v>175</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D181" s="1" t="s">
         <v>180</v>
@@ -46747,7 +46751,7 @@
         <v>175</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D182" s="1" t="s">
         <v>181</v>
@@ -46801,7 +46805,7 @@
         <v>175</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D183" s="1" t="s">
         <v>182</v>
@@ -46855,7 +46859,7 @@
         <v>175</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D184" s="1" t="s">
         <v>183</v>
@@ -46909,7 +46913,7 @@
         <v>175</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D185" s="1" t="s">
         <v>184</v>
@@ -46963,7 +46967,7 @@
         <v>175</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D186" s="1" t="s">
         <v>185</v>
@@ -47017,7 +47021,7 @@
         <v>175</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D187" s="1" t="s">
         <v>186</v>
@@ -47071,7 +47075,7 @@
         <v>175</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D188" s="1" t="s">
         <v>187</v>
@@ -47125,7 +47129,7 @@
         <v>175</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D189" s="1" t="s">
         <v>188</v>
@@ -47179,7 +47183,7 @@
         <v>175</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D190" s="1" t="s">
         <v>189</v>
@@ -47233,7 +47237,7 @@
         <v>190</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D191" s="1" t="s">
         <v>191</v>
@@ -47287,7 +47291,7 @@
         <v>190</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D192" s="1" t="s">
         <v>192</v>
@@ -47341,7 +47345,7 @@
         <v>190</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D193" s="1" t="s">
         <v>193</v>
@@ -47395,7 +47399,7 @@
         <v>190</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D194" s="1" t="s">
         <v>194</v>
@@ -47449,7 +47453,7 @@
         <v>190</v>
       </c>
       <c r="C195" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D195" s="1" t="s">
         <v>195</v>
@@ -47503,7 +47507,7 @@
         <v>190</v>
       </c>
       <c r="C196" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D196" s="1" t="s">
         <v>196</v>
@@ -47557,7 +47561,7 @@
         <v>190</v>
       </c>
       <c r="C197" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D197" s="1" t="s">
         <v>197</v>
@@ -47611,7 +47615,7 @@
         <v>190</v>
       </c>
       <c r="C198" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D198" s="1" t="s">
         <v>198</v>
@@ -47665,7 +47669,7 @@
         <v>190</v>
       </c>
       <c r="C199" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D199" s="1" t="s">
         <v>199</v>
@@ -47719,7 +47723,7 @@
         <v>190</v>
       </c>
       <c r="C200" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D200" s="1" t="s">
         <v>200</v>
@@ -47773,7 +47777,7 @@
         <v>190</v>
       </c>
       <c r="C201" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D201" s="1" t="s">
         <v>190</v>
@@ -47827,7 +47831,7 @@
         <v>190</v>
       </c>
       <c r="C202" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D202" s="1" t="s">
         <v>201</v>
@@ -47881,7 +47885,7 @@
         <v>190</v>
       </c>
       <c r="C203" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D203" s="1" t="s">
         <v>202</v>
@@ -47935,7 +47939,7 @@
         <v>203</v>
       </c>
       <c r="C204" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D204" s="1" t="s">
         <v>204</v>
@@ -47989,7 +47993,7 @@
         <v>203</v>
       </c>
       <c r="C205" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D205" s="1" t="s">
         <v>205</v>
@@ -48045,7 +48049,7 @@
         <v>203</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D206" s="1" t="s">
         <v>206</v>
@@ -48099,7 +48103,7 @@
         <v>203</v>
       </c>
       <c r="C207" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D207" s="1" t="s">
         <v>207</v>
@@ -48153,13 +48157,13 @@
         <v>203</v>
       </c>
       <c r="C208" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D208" s="1" t="s">
         <v>55</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F208" s="2">
         <v>6.3</v>
@@ -48209,7 +48213,7 @@
         <v>203</v>
       </c>
       <c r="C209" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D209" s="1" t="s">
         <v>208</v>
@@ -48263,7 +48267,7 @@
         <v>203</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D210" s="1" t="s">
         <v>209</v>
@@ -48317,7 +48321,7 @@
         <v>203</v>
       </c>
       <c r="C211" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D211" s="1" t="s">
         <v>210</v>
@@ -48373,7 +48377,7 @@
         <v>203</v>
       </c>
       <c r="C212" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D212" s="1" t="s">
         <v>211</v>
@@ -48429,7 +48433,7 @@
         <v>203</v>
       </c>
       <c r="C213" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D213" s="1" t="s">
         <v>212</v>
@@ -48485,7 +48489,7 @@
         <v>203</v>
       </c>
       <c r="C214" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D214" s="1" t="s">
         <v>190</v>
@@ -48539,7 +48543,7 @@
         <v>203</v>
       </c>
       <c r="C215" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D215" s="1" t="s">
         <v>213</v>
@@ -48595,7 +48599,7 @@
         <v>203</v>
       </c>
       <c r="C216" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D216" s="1" t="s">
         <v>214</v>
@@ -48649,7 +48653,7 @@
         <v>215</v>
       </c>
       <c r="C217" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D217" s="1" t="s">
         <v>216</v>
@@ -48703,7 +48707,7 @@
         <v>215</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D218" s="1" t="s">
         <v>217</v>
@@ -48757,7 +48761,7 @@
         <v>215</v>
       </c>
       <c r="C219" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D219" s="1" t="s">
         <v>218</v>
@@ -48811,7 +48815,7 @@
         <v>215</v>
       </c>
       <c r="C220" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D220" s="1" t="s">
         <v>219</v>
@@ -48865,7 +48869,7 @@
         <v>215</v>
       </c>
       <c r="C221" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D221" s="1" t="s">
         <v>126</v>
@@ -48921,7 +48925,7 @@
         <v>215</v>
       </c>
       <c r="C222" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D222" s="1" t="s">
         <v>220</v>
@@ -48975,7 +48979,7 @@
         <v>215</v>
       </c>
       <c r="C223" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D223" s="1" t="s">
         <v>221</v>
@@ -49031,7 +49035,7 @@
         <v>215</v>
       </c>
       <c r="C224" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D224" s="1" t="s">
         <v>222</v>
@@ -49085,7 +49089,7 @@
         <v>215</v>
       </c>
       <c r="C225" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D225" s="1" t="s">
         <v>223</v>
@@ -49139,7 +49143,7 @@
         <v>215</v>
       </c>
       <c r="C226" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D226" s="1" t="s">
         <v>66</v>
@@ -49195,7 +49199,7 @@
         <v>215</v>
       </c>
       <c r="C227" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D227" s="1" t="s">
         <v>37</v>
@@ -49249,7 +49253,7 @@
         <v>215</v>
       </c>
       <c r="C228" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D228" s="1" t="s">
         <v>224</v>
@@ -49305,7 +49309,7 @@
         <v>215</v>
       </c>
       <c r="C229" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D229" s="1" t="s">
         <v>225</v>
@@ -49359,7 +49363,7 @@
         <v>215</v>
       </c>
       <c r="C230" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D230" s="1" t="s">
         <v>226</v>
@@ -49413,7 +49417,7 @@
         <v>215</v>
       </c>
       <c r="C231" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D231" s="1" t="s">
         <v>227</v>
@@ -49467,7 +49471,7 @@
         <v>215</v>
       </c>
       <c r="C232" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D232" s="1" t="s">
         <v>228</v>
@@ -49521,7 +49525,7 @@
         <v>215</v>
       </c>
       <c r="C233" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D233" s="1" t="s">
         <v>229</v>
@@ -49575,7 +49579,7 @@
         <v>215</v>
       </c>
       <c r="C234" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D234" s="1" t="s">
         <v>230</v>
@@ -49629,7 +49633,7 @@
         <v>215</v>
       </c>
       <c r="C235" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D235" s="1" t="s">
         <v>231</v>
@@ -49683,7 +49687,7 @@
         <v>215</v>
       </c>
       <c r="C236" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D236" s="1" t="s">
         <v>232</v>
@@ -49739,7 +49743,7 @@
         <v>215</v>
       </c>
       <c r="C237" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D237" s="1" t="s">
         <v>8</v>
@@ -49793,7 +49797,7 @@
         <v>233</v>
       </c>
       <c r="C238" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D238" s="1" t="s">
         <v>132</v>
@@ -49849,7 +49853,7 @@
         <v>233</v>
       </c>
       <c r="C239" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D239" s="1" t="s">
         <v>29</v>
@@ -49905,7 +49909,7 @@
         <v>233</v>
       </c>
       <c r="C240" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D240" s="1" t="s">
         <v>234</v>
@@ -49961,7 +49965,7 @@
         <v>233</v>
       </c>
       <c r="C241" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D241" s="1" t="s">
         <v>235</v>
@@ -50017,7 +50021,7 @@
         <v>233</v>
       </c>
       <c r="C242" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D242" s="1" t="s">
         <v>236</v>
@@ -50073,7 +50077,7 @@
         <v>233</v>
       </c>
       <c r="C243" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D243" s="1" t="s">
         <v>237</v>
@@ -50129,7 +50133,7 @@
         <v>233</v>
       </c>
       <c r="C244" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D244" s="1" t="s">
         <v>238</v>
@@ -50185,7 +50189,7 @@
         <v>233</v>
       </c>
       <c r="C245" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D245" s="1" t="s">
         <v>136</v>
@@ -50241,7 +50245,7 @@
         <v>233</v>
       </c>
       <c r="C246" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D246" s="1" t="s">
         <v>239</v>
@@ -50297,7 +50301,7 @@
         <v>233</v>
       </c>
       <c r="C247" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D247" s="1" t="s">
         <v>240</v>
@@ -50353,7 +50357,7 @@
         <v>233</v>
       </c>
       <c r="C248" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D248" s="1" t="s">
         <v>241</v>
@@ -50409,7 +50413,7 @@
         <v>233</v>
       </c>
       <c r="C249" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D249" s="1" t="s">
         <v>242</v>
@@ -50465,7 +50469,7 @@
         <v>233</v>
       </c>
       <c r="C250" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D250" s="1" t="s">
         <v>243</v>
@@ -50521,7 +50525,7 @@
         <v>233</v>
       </c>
       <c r="C251" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D251" s="1" t="s">
         <v>244</v>
@@ -50577,7 +50581,7 @@
         <v>233</v>
       </c>
       <c r="C252" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D252" s="1" t="s">
         <v>245</v>
@@ -50633,7 +50637,7 @@
         <v>233</v>
       </c>
       <c r="C253" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D253" s="1" t="s">
         <v>246</v>
@@ -50689,7 +50693,7 @@
         <v>233</v>
       </c>
       <c r="C254" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D254" s="1" t="s">
         <v>155</v>
@@ -50745,7 +50749,7 @@
         <v>233</v>
       </c>
       <c r="C255" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D255" s="1" t="s">
         <v>247</v>
@@ -50801,7 +50805,7 @@
         <v>248</v>
       </c>
       <c r="C256" s="6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D256" s="1" t="s">
         <v>249</v>
@@ -50855,7 +50859,7 @@
         <v>248</v>
       </c>
       <c r="C257" s="6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D257" s="1" t="s">
         <v>13</v>
@@ -50906,10 +50910,10 @@
         <v>256</v>
       </c>
       <c r="B258" s="6" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C258" s="6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D258" s="1" t="s">
         <v>250</v>
@@ -50963,7 +50967,7 @@
         <v>248</v>
       </c>
       <c r="C259" s="6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D259" s="1" t="s">
         <v>248</v>
@@ -51019,7 +51023,7 @@
         <v>248</v>
       </c>
       <c r="C260" s="6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D260" s="1" t="s">
         <v>251</v>
@@ -51073,7 +51077,7 @@
         <v>248</v>
       </c>
       <c r="C261" s="6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D261" s="1" t="s">
         <v>252</v>
@@ -51127,7 +51131,7 @@
         <v>253</v>
       </c>
       <c r="C262" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D262" s="1" t="s">
         <v>254</v>
@@ -51181,7 +51185,7 @@
         <v>253</v>
       </c>
       <c r="C263" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D263" s="1" t="s">
         <v>255</v>
@@ -51235,7 +51239,7 @@
         <v>253</v>
       </c>
       <c r="C264" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D264" s="1" t="s">
         <v>256</v>
@@ -51289,7 +51293,7 @@
         <v>253</v>
       </c>
       <c r="C265" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D265" s="1" t="s">
         <v>257</v>
@@ -51345,7 +51349,7 @@
         <v>253</v>
       </c>
       <c r="C266" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D266" s="1" t="s">
         <v>258</v>
@@ -51399,7 +51403,7 @@
         <v>253</v>
       </c>
       <c r="C267" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D267" s="1" t="s">
         <v>259</v>
@@ -51453,7 +51457,7 @@
         <v>253</v>
       </c>
       <c r="C268" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D268" s="1" t="s">
         <v>77</v>
@@ -51507,7 +51511,7 @@
         <v>253</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D269" s="1" t="s">
         <v>260</v>
@@ -51561,7 +51565,7 @@
         <v>253</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D270" s="1" t="s">
         <v>261</v>
@@ -51615,7 +51619,7 @@
         <v>253</v>
       </c>
       <c r="C271" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D271" s="1" t="s">
         <v>262</v>
@@ -51669,7 +51673,7 @@
         <v>253</v>
       </c>
       <c r="C272" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D272" s="1" t="s">
         <v>263</v>
@@ -51725,7 +51729,7 @@
         <v>253</v>
       </c>
       <c r="C273" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D273" s="1" t="s">
         <v>264</v>
@@ -51779,7 +51783,7 @@
         <v>253</v>
       </c>
       <c r="C274" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D274" s="1" t="s">
         <v>265</v>
@@ -51833,7 +51837,7 @@
         <v>253</v>
       </c>
       <c r="C275" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D275" s="1" t="s">
         <v>266</v>
@@ -51887,7 +51891,7 @@
         <v>253</v>
       </c>
       <c r="C276" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D276" s="1" t="s">
         <v>267</v>
@@ -51943,7 +51947,7 @@
         <v>253</v>
       </c>
       <c r="C277" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D277" s="1" t="s">
         <v>68</v>
@@ -51997,7 +52001,7 @@
         <v>93</v>
       </c>
       <c r="C278" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D278" s="1" t="s">
         <v>268</v>
@@ -52053,7 +52057,7 @@
         <v>93</v>
       </c>
       <c r="C279" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D279" s="1" t="s">
         <v>269</v>
@@ -52107,7 +52111,7 @@
         <v>93</v>
       </c>
       <c r="C280" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D280" s="1" t="s">
         <v>270</v>
@@ -52161,7 +52165,7 @@
         <v>93</v>
       </c>
       <c r="C281" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D281" s="1" t="s">
         <v>50</v>
@@ -52215,7 +52219,7 @@
         <v>93</v>
       </c>
       <c r="C282" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D282" s="1" t="s">
         <v>271</v>
@@ -52269,7 +52273,7 @@
         <v>93</v>
       </c>
       <c r="C283" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D283" s="1" t="s">
         <v>148</v>
@@ -52325,7 +52329,7 @@
         <v>93</v>
       </c>
       <c r="C284" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D284" s="1" t="s">
         <v>149</v>
@@ -52379,7 +52383,7 @@
         <v>93</v>
       </c>
       <c r="C285" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D285" s="1" t="s">
         <v>272</v>
@@ -52433,7 +52437,7 @@
         <v>93</v>
       </c>
       <c r="C286" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D286" s="1" t="s">
         <v>273</v>
@@ -52487,7 +52491,7 @@
         <v>93</v>
       </c>
       <c r="C287" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D287" s="1" t="s">
         <v>274</v>
@@ -52543,7 +52547,7 @@
         <v>93</v>
       </c>
       <c r="C288" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D288" s="1" t="s">
         <v>275</v>
@@ -52599,7 +52603,7 @@
         <v>93</v>
       </c>
       <c r="C289" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D289" s="1" t="s">
         <v>276</v>
@@ -52653,7 +52657,7 @@
         <v>93</v>
       </c>
       <c r="C290" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D290" s="1" t="s">
         <v>277</v>
@@ -52709,7 +52713,7 @@
         <v>93</v>
       </c>
       <c r="C291" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D291" s="1" t="s">
         <v>278</v>
@@ -52765,7 +52769,7 @@
         <v>93</v>
       </c>
       <c r="C292" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D292" s="1" t="s">
         <v>279</v>
@@ -52821,7 +52825,7 @@
         <v>93</v>
       </c>
       <c r="C293" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D293" s="1" t="s">
         <v>280</v>
@@ -52877,7 +52881,7 @@
         <v>93</v>
       </c>
       <c r="C294" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D294" s="1" t="s">
         <v>281</v>
@@ -52933,7 +52937,7 @@
         <v>93</v>
       </c>
       <c r="C295" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D295" s="1" t="s">
         <v>282</v>
@@ -52989,7 +52993,7 @@
         <v>93</v>
       </c>
       <c r="C296" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D296" s="1" t="s">
         <v>283</v>
@@ -53045,7 +53049,7 @@
         <v>93</v>
       </c>
       <c r="C297" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D297" s="1" t="s">
         <v>284</v>
@@ -53099,7 +53103,7 @@
         <v>93</v>
       </c>
       <c r="C298" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D298" s="1" t="s">
         <v>285</v>
@@ -53155,7 +53159,7 @@
         <v>93</v>
       </c>
       <c r="C299" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D299" s="1" t="s">
         <v>286</v>
@@ -53211,7 +53215,7 @@
         <v>93</v>
       </c>
       <c r="C300" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D300" s="1" t="s">
         <v>213</v>
@@ -53267,13 +53271,13 @@
         <v>93</v>
       </c>
       <c r="C301" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D301" s="1" t="s">
         <v>287</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="F301" s="2">
         <v>-0.1</v>
@@ -53323,7 +53327,7 @@
         <v>288</v>
       </c>
       <c r="C302" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D302" s="1" t="s">
         <v>289</v>
@@ -53377,7 +53381,7 @@
         <v>288</v>
       </c>
       <c r="C303" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D303" s="1" t="s">
         <v>290</v>
@@ -53431,7 +53435,7 @@
         <v>288</v>
       </c>
       <c r="C304" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D304" s="1" t="s">
         <v>291</v>
@@ -53485,7 +53489,7 @@
         <v>288</v>
       </c>
       <c r="C305" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D305" s="1" t="s">
         <v>216</v>
@@ -53539,7 +53543,7 @@
         <v>288</v>
       </c>
       <c r="C306" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D306" s="1" t="s">
         <v>292</v>
@@ -53593,7 +53597,7 @@
         <v>288</v>
       </c>
       <c r="C307" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D307" s="1" t="s">
         <v>293</v>
@@ -53647,7 +53651,7 @@
         <v>288</v>
       </c>
       <c r="C308" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D308" s="1" t="s">
         <v>294</v>
@@ -53701,7 +53705,7 @@
         <v>288</v>
       </c>
       <c r="C309" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D309" s="1" t="s">
         <v>295</v>
@@ -53755,7 +53759,7 @@
         <v>288</v>
       </c>
       <c r="C310" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D310" s="1" t="s">
         <v>296</v>
@@ -53809,7 +53813,7 @@
         <v>288</v>
       </c>
       <c r="C311" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D311" s="1" t="s">
         <v>177</v>
@@ -53863,7 +53867,7 @@
         <v>288</v>
       </c>
       <c r="C312" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D312" s="1" t="s">
         <v>297</v>
@@ -53917,7 +53921,7 @@
         <v>288</v>
       </c>
       <c r="C313" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D313" s="1" t="s">
         <v>298</v>
@@ -53971,7 +53975,7 @@
         <v>288</v>
       </c>
       <c r="C314" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D314" s="1" t="s">
         <v>299</v>
@@ -54025,7 +54029,7 @@
         <v>288</v>
       </c>
       <c r="C315" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D315" s="1" t="s">
         <v>300</v>
@@ -54079,7 +54083,7 @@
         <v>288</v>
       </c>
       <c r="C316" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D316" s="1" t="s">
         <v>301</v>
@@ -54133,7 +54137,7 @@
         <v>288</v>
       </c>
       <c r="C317" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D317" s="1" t="s">
         <v>302</v>
@@ -54187,7 +54191,7 @@
         <v>288</v>
       </c>
       <c r="C318" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D318" s="1" t="s">
         <v>303</v>
@@ -54241,7 +54245,7 @@
         <v>288</v>
       </c>
       <c r="C319" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D319" s="1" t="s">
         <v>304</v>
